--- a/test_cases_n5_n12.xlsx
+++ b/test_cases_n5_n12.xlsx
@@ -7,13 +7,14 @@
     <sheet sheetId="1" name="Kịch bản kiểm thử" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="Quản trị hệ thống" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="Luồng nghiệp vụ liên thông" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Kịch bản API" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5398" uniqueCount="2382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5501" uniqueCount="2433">
   <si>
     <t>KỊCH BẢN KIỂM THỬ *</t>
   </si>
@@ -9106,6 +9107,185 @@
 2. Tuyệt đối không tính gộp số thuế "8000" triệu của Chủ đầu tư B (kỳ Quý II/2026) vào biểu tổng hợp Quý I/2026.
 3. Tại bước 8 (xem Quý II/2026): Số liệu tổng hợp thuế chỉ hiển thị "8000" triệu của Chủ đầu tư B, không gộp số liệu của Quý I.
 4. Hệ thống phân tách độc lập và chính xác số liệu tổng hợp SUM và AVG của từng kỳ báo cáo riêng biệt.</t>
+  </si>
+  <si>
+    <t>API Testing</t>
+  </si>
+  <si>
+    <t>KỊCH BẢN KIỂM THỬ API - TỔNG QUAN DỰ ÁN NHÀ Ở (N3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   1. CHỨC NĂNG TỔNG QUAN VỀ DỰ ÁN (N3) - API</t>
+  </si>
+  <si>
+    <t>API_N3_001</t>
+  </si>
+  <si>
+    <t>Kiểm tra lấy dữ liệu tổng quan thành công (Không Token - Cổng Public)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Gửi request GET tới endpoint `/report_api_v2/api/v1/public/bds/n3/tong-quan-du-an`.
+2. Không truyền header `Authorization`.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. HTTP Status Code = 200 OK.
+2. Trả về số liệu tổng hợp của toàn hệ thống (tất cả các tổ chức/đơn vị).
+3. Response body có đủ 6 chỉ tiêu: `chap_thuan_chu_truong`, `cap_phep_xay_dung`, `dang_trien_khai`, `da_hoan_thanh`, `chuyen_nhuong`, `bds_du_dieu_kien_kd`.</t>
+  </si>
+  <si>
+    <t>API_N3_002</t>
+  </si>
+  <si>
+    <t>Kiểm tra lấy dữ liệu tổng quan thành công (Có Token - Báo cáo nội bộ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Gọi API Login thành công để lấy `token`.
+2. Gửi request GET tới `/tong-quan-du-an`.
+3. Truyền header `Authorization: Bearer &lt;token&gt;`.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. HTTP Status Code = 200 OK.
+2. Dữ liệu trả về chỉ chứa thống kê của các dự án thuộc đơn vị/tổ chức hiện tại của user.
+3. Đảm bảo dữ liệu bị cô lập hoàn toàn (Data isolation), không chứa dữ liệu của địa phương khác.</t>
+  </si>
+  <si>
+    <t>API_N3_003</t>
+  </si>
+  <si>
+    <t>Kiểm tra cấu trúc dữ liệu trả về (Response Schema Validation)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Gửi request hợp lệ tới API (có token hoặc không token).
+2. Phân tích cấu trúc JSON trả về.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. JSON trả về đúng chuẩn.
+2. Các trường thống kê số lượng đều là định dạng Số (Number).
+3. `danh_sach_chap_thuan_chu_truong` và `danh_sach_cap_phep_xay_dung` là mảng (Array) chứa các object `{ma_du_an, ngay_cap}`.</t>
+  </si>
+  <si>
+    <t>API_N3_004</t>
+  </si>
+  <si>
+    <t>Kiểm tra API với Token không hợp lệ (Invalid Token)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Gửi request GET tới endpoint.
+2. Truyền header `Authorization: Bearer &lt;token_sai_hoac_da_het_han&gt;`.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. HTTP Status Code = 401 Unauthorized.
+2. Hiển thị thông báo lỗi Token không hợp lệ, không trả về dữ liệu rác hoặc fallback về public data.</t>
+  </si>
+  <si>
+    <t>API_N3_005</t>
+  </si>
+  <si>
+    <t>Kiểm tra API với SQL Injection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Gửi request GET tới endpoint.
+2. Chèn payload SQL Injection vào header hoặc path parameters (nếu có bổ sung).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Hệ thống chặn request và trả về lỗi an toàn (ví dụ: HTTP 400 Bad Request).
+2. Không làm lộ cấu trúc cơ sở dữ liệu.</t>
+  </si>
+  <si>
+    <t>API_N3_006</t>
+  </si>
+  <si>
+    <t>Kiểm tra Response Time (Hiệu năng cơ bản)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Gửi request GET (không token) để load toàn bộ dữ liệu hệ thống.
+2. Đo đạc thời gian nhận được response.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. HTTP Status Code = 200 OK.
+2. Thời gian phản hồi (Response Time) nằm trong ngưỡng chấp nhận được (&lt; 3 giây) kể cả khi dữ liệu hệ thống lớn.</t>
+  </si>
+  <si>
+    <t>API_N3_007</t>
+  </si>
+  <si>
+    <t>Kiểm tra logic tính "Số lượng dự án được chấp thuận chủ trương đầu tư" (Chỉ tiêu 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Tạo 1 bản ghi dự án có đính kèm file hoặc có ngày cấp ở dòng tài liệu chứa từ khóa "chấp thuận chủ trương đầu tư".
+2. Gửi request GET kiểm tra.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. `chap_thuan_chu_truong` đếm tăng 1.
+2. API trả về thuộc tính `danh_sach_chap_thuan_chu_truong` chứa mảng các object `{ma_du_an, ngay_cap}` tương ứng với dữ liệu vừa nhập (phục vụ lọc theo thời gian).</t>
+  </si>
+  <si>
+    <t>API_N3_008</t>
+  </si>
+  <si>
+    <t>Kiểm tra logic tính "Số lượng dự án được cấp phép xây dựng" (Chỉ tiêu 2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Tạo 1 bản ghi dự án có đính kèm file hoặc ngày cấp ở dòng tài liệu chứa từ khóa "giấy phép xây dựng".
+2. Gửi request GET kiểm tra.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. `cap_phep_xay_dung` đếm tăng 1.
+2. `danh_sach_cap_phep_xay_dung` trả về `{ma_du_an, ngay_cap}` hợp lệ (phục vụ lọc thời gian).</t>
+  </si>
+  <si>
+    <t>API_N3_009</t>
+  </si>
+  <si>
+    <t>Kiểm tra logic tính "Số dự án đang triển khai xây dựng" (Chỉ tiêu 3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Khai báo 1 dự án với tổng "Số lượng" (Quy mô - Tab 1) lớn hơn "Lũy kế số lượng hoàn thành" (Tiến độ - Tab 4).
+2. Gửi request kiểm tra kết quả.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. API đếm tăng 1 cho chỉ tiêu `dang_trien_khai`.
+2. (Chỉ tiêu `da_hoan_thanh` không tăng với dự án này).</t>
+  </si>
+  <si>
+    <t>API_N3_010</t>
+  </si>
+  <si>
+    <t>Kiểm tra logic tính "Số dự án đã hoàn thành đưa vào sử dụng" (Chỉ tiêu 4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Khai báo dự án với tổng "Số lượng" (Quy mô - Tab 1) bằng chính xác "Lũy kế số lượng hoàn thành" (Tiến độ - Tab 4) - kể cả trường hợp 0 = 0.
+2. Gửi request kiểm tra.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. `da_hoan_thanh` đếm tăng 1.
+2. `dang_trien_khai` không tăng.</t>
+  </si>
+  <si>
+    <t>API_N3_011</t>
+  </si>
+  <si>
+    <t>Kiểm tra logic đếm "Số lượng dự án được chuyển nhượng" (Chỉ tiêu 5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Khai báo 1 dự án và nhập dữ liệu vào trường `so_quyet_dinh_cho_phep_chuyen_nhuong` ở Tab 5 (bỏ trống các trường khác ở tab 5).
+2. Gửi request GET.</t>
+  </si>
+  <si>
+    <t>1. Chỉ tiêu `chuyen_nhuong` tăng 1 (chỉ cần trường Số quyết định có dữ liệu là đủ điều kiện đếm, không cần check các bảng quy mô).</t>
+  </si>
+  <si>
+    <t>API_N3_012</t>
+  </si>
+  <si>
+    <t>Kiểm tra logic tính "Số lượng BĐS đủ điều kiện đưa vào kinh doanh" (Chỉ tiêu 6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Khai báo dự án có nhiều loại hình BĐS, nhập giá trị "Lũy kế số lượng đủ điều kiện kinh doanh" (Tab 3).
+2. Gửi request GET kiểm tra.</t>
+  </si>
+  <si>
+    <t>1. `bds_du_dieu_kien_kd` trả về giá trị tổng số lượng BĐS cộng dồn từ tất cả các dòng (SUM các `luy_ke_so_luong_du_dieu_kien_kinh_doanh`), KHÔNG phải đếm số lượng dự án.</t>
   </si>
 </sst>
 </file>
@@ -28388,4 +28568,412 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G24"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="3" max="4" width="55" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="45" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1"/>
+    </row>
+    <row r="2" ht="20" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>2382</v>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="4">
+        <f>=COUNTIF(E11:E2000, "P")</f>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="4">
+        <f>=COUNTIF(E11:E2000, "F")</f>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="4">
+        <f>=COUNTIF(E11:E2000, "PE")</f>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="4">
+        <f>=COUNTIF(E11:E2000, "Chưa thực hiện")</f>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="4">
+        <f>=SUM(D4:D7)</f>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>2383</v>
+      </c>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+    </row>
+    <row r="12" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>2384</v>
+      </c>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>2385</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>2386</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>2387</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>2388</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
+        <v>2389</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>2390</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>2391</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>2392</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
+        <v>2393</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>2394</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>2395</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>2396</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="8" t="s">
+        <v>2397</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>2398</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>2399</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>2400</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="8" t="s">
+        <v>2401</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>2402</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>2403</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>2404</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="8" t="s">
+        <v>2405</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>2406</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>2407</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>2408</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="8" t="s">
+        <v>2409</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>2410</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>2411</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>2412</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="8" t="s">
+        <v>2413</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>2414</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>2415</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>2416</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="8" t="s">
+        <v>2417</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>2418</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>2419</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>2420</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="8" t="s">
+        <v>2421</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>2422</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>2423</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>2424</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="8" t="s">
+        <v>2425</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>2426</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>2427</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>2428</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="8" t="s">
+        <v>2429</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>2430</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>2431</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>2432</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A12:G12"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
 </file>
--- a/test_cases_n5_n12.xlsx
+++ b/test_cases_n5_n12.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Kịch bản kiểm thử" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="Module Báo cáo" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="Quản trị hệ thống" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="Luồng nghiệp vụ liên thông" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="Kịch bản API" state="visible" r:id="rId7"/>

--- a/test_cases_n5_n12.xlsx
+++ b/test_cases_n5_n12.xlsx
@@ -9837,6 +9837,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
   <dimension ref="A1:M637"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
@@ -9990,7 +9993,7 @@
       <c r="L12" s="7"/>
       <c r="M12" s="7"/>
     </row>
-    <row r="13" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A13" s="8" t="s">
         <v>22</v>
       </c>
@@ -10007,7 +10010,7 @@
       <c r="L13" s="8"/>
       <c r="M13" s="8"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A14" s="9" t="s">
         <v>23</v>
       </c>
@@ -10048,7 +10051,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A15" s="9" t="s">
         <v>29</v>
       </c>
@@ -10089,7 +10092,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A16" s="9" t="s">
         <v>33</v>
       </c>
@@ -10130,7 +10133,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A17" s="9" t="s">
         <v>37</v>
       </c>
@@ -10171,7 +10174,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A18" s="9" t="s">
         <v>41</v>
       </c>
@@ -10212,7 +10215,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A19" s="9" t="s">
         <v>45</v>
       </c>
@@ -10253,7 +10256,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A20" s="9" t="s">
         <v>49</v>
       </c>
@@ -10294,7 +10297,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A21" s="9" t="s">
         <v>53</v>
       </c>
@@ -10335,7 +10338,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A22" s="9" t="s">
         <v>57</v>
       </c>
@@ -10376,7 +10379,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A23" s="9" t="s">
         <v>61</v>
       </c>
@@ -10417,7 +10420,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A24" s="9" t="s">
         <v>64</v>
       </c>
@@ -10458,7 +10461,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A25" s="9" t="s">
         <v>68</v>
       </c>
@@ -10499,7 +10502,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A26" s="9" t="s">
         <v>71</v>
       </c>
@@ -10540,7 +10543,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A27" s="9" t="s">
         <v>75</v>
       </c>
@@ -10581,7 +10584,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A28" s="9" t="s">
         <v>78</v>
       </c>
@@ -10622,7 +10625,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A29" s="9" t="s">
         <v>82</v>
       </c>
@@ -10663,7 +10666,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A30" s="9" t="s">
         <v>86</v>
       </c>
@@ -10704,7 +10707,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A31" s="9" t="s">
         <v>90</v>
       </c>
@@ -10745,7 +10748,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A32" s="9" t="s">
         <v>93</v>
       </c>
@@ -10786,7 +10789,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A33" s="9" t="s">
         <v>97</v>
       </c>
@@ -10827,7 +10830,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A34" s="9" t="s">
         <v>100</v>
       </c>
@@ -10868,7 +10871,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A35" s="9" t="s">
         <v>104</v>
       </c>
@@ -10909,7 +10912,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A36" s="9" t="s">
         <v>108</v>
       </c>
@@ -10950,7 +10953,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A37" s="9" t="s">
         <v>112</v>
       </c>
@@ -10991,7 +10994,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A38" s="9" t="s">
         <v>116</v>
       </c>
@@ -11032,7 +11035,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A39" s="9" t="s">
         <v>120</v>
       </c>
@@ -11073,7 +11076,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="40" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="40" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A40" s="8" t="s">
         <v>123</v>
       </c>
@@ -11090,7 +11093,7 @@
       <c r="L40" s="8"/>
       <c r="M40" s="8"/>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A41" s="9" t="s">
         <v>124</v>
       </c>
@@ -11131,7 +11134,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A42" s="9" t="s">
         <v>128</v>
       </c>
@@ -11172,7 +11175,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A43" s="9" t="s">
         <v>132</v>
       </c>
@@ -11230,7 +11233,7 @@
       <c r="L44" s="7"/>
       <c r="M44" s="7"/>
     </row>
-    <row r="45" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="45" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A45" s="8" t="s">
         <v>22</v>
       </c>
@@ -11247,7 +11250,7 @@
       <c r="L45" s="8"/>
       <c r="M45" s="8"/>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A46" s="9" t="s">
         <v>137</v>
       </c>
@@ -11288,7 +11291,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A47" s="9" t="s">
         <v>139</v>
       </c>
@@ -11329,7 +11332,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A48" s="9" t="s">
         <v>141</v>
       </c>
@@ -11370,7 +11373,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A49" s="9" t="s">
         <v>143</v>
       </c>
@@ -11411,7 +11414,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A50" s="9" t="s">
         <v>145</v>
       </c>
@@ -11452,7 +11455,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A51" s="9" t="s">
         <v>147</v>
       </c>
@@ -11493,7 +11496,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A52" s="9" t="s">
         <v>149</v>
       </c>
@@ -11534,7 +11537,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A53" s="9" t="s">
         <v>153</v>
       </c>
@@ -11575,7 +11578,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A54" s="9" t="s">
         <v>157</v>
       </c>
@@ -11616,7 +11619,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A55" s="9" t="s">
         <v>161</v>
       </c>
@@ -11657,7 +11660,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A56" s="9" t="s">
         <v>164</v>
       </c>
@@ -11698,7 +11701,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A57" s="9" t="s">
         <v>168</v>
       </c>
@@ -11739,7 +11742,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A58" s="9" t="s">
         <v>171</v>
       </c>
@@ -11780,7 +11783,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A59" s="9" t="s">
         <v>175</v>
       </c>
@@ -11821,7 +11824,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A60" s="9" t="s">
         <v>178</v>
       </c>
@@ -11862,7 +11865,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A61" s="9" t="s">
         <v>182</v>
       </c>
@@ -11903,7 +11906,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A62" s="9" t="s">
         <v>185</v>
       </c>
@@ -11944,7 +11947,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A63" s="9" t="s">
         <v>189</v>
       </c>
@@ -11985,7 +11988,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="64" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="64" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A64" s="8" t="s">
         <v>123</v>
       </c>
@@ -12002,7 +12005,7 @@
       <c r="L64" s="8"/>
       <c r="M64" s="8"/>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A65" s="9" t="s">
         <v>192</v>
       </c>
@@ -12043,7 +12046,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A66" s="9" t="s">
         <v>196</v>
       </c>
@@ -12084,7 +12087,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A67" s="9" t="s">
         <v>200</v>
       </c>
@@ -12142,7 +12145,7 @@
       <c r="L68" s="7"/>
       <c r="M68" s="7"/>
     </row>
-    <row r="69" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="69" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A69" s="8" t="s">
         <v>22</v>
       </c>
@@ -12159,7 +12162,7 @@
       <c r="L69" s="8"/>
       <c r="M69" s="8"/>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A70" s="9" t="s">
         <v>205</v>
       </c>
@@ -12200,7 +12203,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A71" s="9" t="s">
         <v>207</v>
       </c>
@@ -12241,7 +12244,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A72" s="9" t="s">
         <v>209</v>
       </c>
@@ -12282,7 +12285,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A73" s="9" t="s">
         <v>211</v>
       </c>
@@ -12323,7 +12326,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A74" s="9" t="s">
         <v>213</v>
       </c>
@@ -12364,7 +12367,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A75" s="9" t="s">
         <v>215</v>
       </c>
@@ -12405,7 +12408,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A76" s="9" t="s">
         <v>217</v>
       </c>
@@ -12446,7 +12449,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A77" s="9" t="s">
         <v>221</v>
       </c>
@@ -12487,7 +12490,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A78" s="9" t="s">
         <v>225</v>
       </c>
@@ -12528,7 +12531,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A79" s="9" t="s">
         <v>229</v>
       </c>
@@ -12569,7 +12572,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A80" s="9" t="s">
         <v>232</v>
       </c>
@@ -12610,7 +12613,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A81" s="9" t="s">
         <v>236</v>
       </c>
@@ -12651,7 +12654,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A82" s="9" t="s">
         <v>239</v>
       </c>
@@ -12692,7 +12695,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A83" s="9" t="s">
         <v>243</v>
       </c>
@@ -12733,7 +12736,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A84" s="9" t="s">
         <v>246</v>
       </c>
@@ -12774,7 +12777,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A85" s="9" t="s">
         <v>250</v>
       </c>
@@ -12815,7 +12818,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A86" s="9" t="s">
         <v>253</v>
       </c>
@@ -12856,7 +12859,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A87" s="9" t="s">
         <v>257</v>
       </c>
@@ -12897,7 +12900,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A88" s="9" t="s">
         <v>260</v>
       </c>
@@ -12938,7 +12941,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A89" s="9" t="s">
         <v>264</v>
       </c>
@@ -12979,7 +12982,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A90" s="9" t="s">
         <v>267</v>
       </c>
@@ -13020,7 +13023,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A91" s="9" t="s">
         <v>271</v>
       </c>
@@ -13061,7 +13064,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A92" s="9" t="s">
         <v>274</v>
       </c>
@@ -13102,7 +13105,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A93" s="9" t="s">
         <v>278</v>
       </c>
@@ -13143,7 +13146,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A94" s="9" t="s">
         <v>281</v>
       </c>
@@ -13184,7 +13187,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A95" s="9" t="s">
         <v>285</v>
       </c>
@@ -13225,7 +13228,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A96" s="9" t="s">
         <v>288</v>
       </c>
@@ -13266,7 +13269,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A97" s="9" t="s">
         <v>292</v>
       </c>
@@ -13307,7 +13310,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A98" s="9" t="s">
         <v>296</v>
       </c>
@@ -13348,7 +13351,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A99" s="9" t="s">
         <v>300</v>
       </c>
@@ -13389,7 +13392,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A100" s="9" t="s">
         <v>303</v>
       </c>
@@ -13430,7 +13433,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A101" s="9" t="s">
         <v>307</v>
       </c>
@@ -13471,7 +13474,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A102" s="9" t="s">
         <v>310</v>
       </c>
@@ -13512,7 +13515,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A103" s="9" t="s">
         <v>314</v>
       </c>
@@ -13553,7 +13556,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A104" s="9" t="s">
         <v>317</v>
       </c>
@@ -13594,7 +13597,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A105" s="9" t="s">
         <v>321</v>
       </c>
@@ -13635,7 +13638,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A106" s="9" t="s">
         <v>324</v>
       </c>
@@ -13676,7 +13679,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A107" s="9" t="s">
         <v>328</v>
       </c>
@@ -13717,7 +13720,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A108" s="9" t="s">
         <v>331</v>
       </c>
@@ -13758,7 +13761,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A109" s="9" t="s">
         <v>335</v>
       </c>
@@ -13799,7 +13802,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A110" s="9" t="s">
         <v>338</v>
       </c>
@@ -13840,7 +13843,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A111" s="9" t="s">
         <v>342</v>
       </c>
@@ -13881,7 +13884,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A112" s="9" t="s">
         <v>345</v>
       </c>
@@ -13922,7 +13925,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A113" s="9" t="s">
         <v>349</v>
       </c>
@@ -13963,7 +13966,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A114" s="9" t="s">
         <v>352</v>
       </c>
@@ -14004,7 +14007,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A115" s="9" t="s">
         <v>356</v>
       </c>
@@ -14045,7 +14048,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="116" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="116" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A116" s="8" t="s">
         <v>123</v>
       </c>
@@ -14062,7 +14065,7 @@
       <c r="L116" s="8"/>
       <c r="M116" s="8"/>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A117" s="9" t="s">
         <v>359</v>
       </c>
@@ -14103,7 +14106,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A118" s="9" t="s">
         <v>363</v>
       </c>
@@ -14144,7 +14147,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A119" s="9" t="s">
         <v>367</v>
       </c>
@@ -14185,7 +14188,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A120" s="9" t="s">
         <v>371</v>
       </c>
@@ -14226,7 +14229,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A121" s="9" t="s">
         <v>375</v>
       </c>
@@ -14267,7 +14270,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A122" s="9" t="s">
         <v>379</v>
       </c>
@@ -14308,7 +14311,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A123" s="9" t="s">
         <v>383</v>
       </c>
@@ -14349,7 +14352,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A124" s="9" t="s">
         <v>387</v>
       </c>
@@ -14390,7 +14393,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A125" s="9" t="s">
         <v>391</v>
       </c>
@@ -14431,7 +14434,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A126" s="9" t="s">
         <v>395</v>
       </c>
@@ -14472,7 +14475,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A127" s="9" t="s">
         <v>399</v>
       </c>
@@ -14513,7 +14516,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A128" s="9" t="s">
         <v>403</v>
       </c>
@@ -14554,7 +14557,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A129" s="9" t="s">
         <v>407</v>
       </c>
@@ -14595,7 +14598,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A130" s="9" t="s">
         <v>411</v>
       </c>
@@ -14636,7 +14639,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A131" s="9" t="s">
         <v>415</v>
       </c>
@@ -14677,7 +14680,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A132" s="9" t="s">
         <v>419</v>
       </c>
@@ -14735,7 +14738,7 @@
       <c r="L133" s="7"/>
       <c r="M133" s="7"/>
     </row>
-    <row r="134" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="134" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A134" s="8" t="s">
         <v>22</v>
       </c>
@@ -14752,7 +14755,7 @@
       <c r="L134" s="8"/>
       <c r="M134" s="8"/>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A135" s="9" t="s">
         <v>424</v>
       </c>
@@ -14793,7 +14796,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A136" s="9" t="s">
         <v>426</v>
       </c>
@@ -14834,7 +14837,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A137" s="9" t="s">
         <v>428</v>
       </c>
@@ -14875,7 +14878,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A138" s="9" t="s">
         <v>430</v>
       </c>
@@ -14916,7 +14919,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A139" s="9" t="s">
         <v>432</v>
       </c>
@@ -14957,7 +14960,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A140" s="9" t="s">
         <v>434</v>
       </c>
@@ -14998,7 +15001,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="141" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="141" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A141" s="8" t="s">
         <v>123</v>
       </c>
@@ -15015,7 +15018,7 @@
       <c r="L141" s="8"/>
       <c r="M141" s="8"/>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A142" s="9" t="s">
         <v>436</v>
       </c>
@@ -15056,7 +15059,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A143" s="9" t="s">
         <v>440</v>
       </c>
@@ -15097,7 +15100,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A144" s="9" t="s">
         <v>444</v>
       </c>
@@ -15155,7 +15158,7 @@
       <c r="L145" s="7"/>
       <c r="M145" s="7"/>
     </row>
-    <row r="146" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="146" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A146" s="8" t="s">
         <v>22</v>
       </c>
@@ -15172,7 +15175,7 @@
       <c r="L146" s="8"/>
       <c r="M146" s="8"/>
     </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A147" s="9" t="s">
         <v>449</v>
       </c>
@@ -15213,7 +15216,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A148" s="9" t="s">
         <v>451</v>
       </c>
@@ -15254,7 +15257,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A149" s="9" t="s">
         <v>453</v>
       </c>
@@ -15295,7 +15298,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A150" s="9" t="s">
         <v>455</v>
       </c>
@@ -15336,7 +15339,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A151" s="9" t="s">
         <v>457</v>
       </c>
@@ -15377,7 +15380,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A152" s="9" t="s">
         <v>459</v>
       </c>
@@ -15418,7 +15421,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A153" s="9" t="s">
         <v>461</v>
       </c>
@@ -15459,7 +15462,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A154" s="9" t="s">
         <v>465</v>
       </c>
@@ -15500,7 +15503,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A155" s="9" t="s">
         <v>468</v>
       </c>
@@ -15541,7 +15544,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A156" s="9" t="s">
         <v>472</v>
       </c>
@@ -15582,7 +15585,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A157" s="9" t="s">
         <v>475</v>
       </c>
@@ -15623,7 +15626,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A158" s="9" t="s">
         <v>479</v>
       </c>
@@ -15664,7 +15667,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A159" s="9" t="s">
         <v>482</v>
       </c>
@@ -15705,7 +15708,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A160" s="9" t="s">
         <v>486</v>
       </c>
@@ -15746,7 +15749,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="161" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="161" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A161" s="8" t="s">
         <v>123</v>
       </c>
@@ -15763,7 +15766,7 @@
       <c r="L161" s="8"/>
       <c r="M161" s="8"/>
     </row>
-    <row r="162" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A162" s="9" t="s">
         <v>489</v>
       </c>
@@ -15804,7 +15807,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A163" s="9" t="s">
         <v>493</v>
       </c>
@@ -15845,7 +15848,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A164" s="9" t="s">
         <v>497</v>
       </c>
@@ -15886,7 +15889,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A165" s="9" t="s">
         <v>501</v>
       </c>
@@ -15927,7 +15930,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="166" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A166" s="9" t="s">
         <v>505</v>
       </c>
@@ -15968,7 +15971,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="167" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A167" s="9" t="s">
         <v>509</v>
       </c>
@@ -16009,7 +16012,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="168" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A168" s="9" t="s">
         <v>513</v>
       </c>
@@ -16050,7 +16053,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="169" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A169" s="9" t="s">
         <v>517</v>
       </c>
@@ -16091,7 +16094,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="170" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A170" s="9" t="s">
         <v>521</v>
       </c>
@@ -16132,7 +16135,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="171" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A171" s="9" t="s">
         <v>525</v>
       </c>
@@ -16173,7 +16176,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="172" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A172" s="9" t="s">
         <v>529</v>
       </c>
@@ -16214,7 +16217,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="173" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A173" s="9" t="s">
         <v>533</v>
       </c>
@@ -16255,7 +16258,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="174" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A174" s="9" t="s">
         <v>537</v>
       </c>
@@ -16296,7 +16299,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="175" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A175" s="9" t="s">
         <v>541</v>
       </c>
@@ -16354,7 +16357,7 @@
       <c r="L176" s="7"/>
       <c r="M176" s="7"/>
     </row>
-    <row r="177" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="177" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A177" s="8" t="s">
         <v>22</v>
       </c>
@@ -16371,7 +16374,7 @@
       <c r="L177" s="8"/>
       <c r="M177" s="8"/>
     </row>
-    <row r="178" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A178" s="9" t="s">
         <v>546</v>
       </c>
@@ -16412,7 +16415,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="179" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A179" s="9" t="s">
         <v>548</v>
       </c>
@@ -16453,7 +16456,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A180" s="9" t="s">
         <v>550</v>
       </c>
@@ -16494,7 +16497,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="181" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A181" s="9" t="s">
         <v>552</v>
       </c>
@@ -16535,7 +16538,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="182" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A182" s="9" t="s">
         <v>554</v>
       </c>
@@ -16576,7 +16579,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="183" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A183" s="9" t="s">
         <v>556</v>
       </c>
@@ -16617,7 +16620,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="184" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A184" s="9" t="s">
         <v>558</v>
       </c>
@@ -16658,7 +16661,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="185" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A185" s="9" t="s">
         <v>562</v>
       </c>
@@ -16699,7 +16702,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="186" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A186" s="9" t="s">
         <v>565</v>
       </c>
@@ -16740,7 +16743,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="187" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A187" s="9" t="s">
         <v>569</v>
       </c>
@@ -16781,7 +16784,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="188" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A188" s="9" t="s">
         <v>572</v>
       </c>
@@ -16822,7 +16825,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="189" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A189" s="9" t="s">
         <v>576</v>
       </c>
@@ -16863,7 +16866,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="190" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A190" s="9" t="s">
         <v>579</v>
       </c>
@@ -16904,7 +16907,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="191" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A191" s="9" t="s">
         <v>582</v>
       </c>
@@ -16945,7 +16948,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="192" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A192" s="9" t="s">
         <v>584</v>
       </c>
@@ -16986,7 +16989,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="193" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A193" s="9" t="s">
         <v>588</v>
       </c>
@@ -17027,7 +17030,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="194" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A194" s="9" t="s">
         <v>591</v>
       </c>
@@ -17068,7 +17071,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="195" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A195" s="9" t="s">
         <v>595</v>
       </c>
@@ -17109,7 +17112,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="196" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A196" s="9" t="s">
         <v>598</v>
       </c>
@@ -17150,7 +17153,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="197" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A197" s="9" t="s">
         <v>602</v>
       </c>
@@ -17191,7 +17194,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="198" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A198" s="9" t="s">
         <v>605</v>
       </c>
@@ -17232,7 +17235,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="199" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A199" s="9" t="s">
         <v>609</v>
       </c>
@@ -17273,7 +17276,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="200" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A200" s="9" t="s">
         <v>612</v>
       </c>
@@ -17314,7 +17317,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="201" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A201" s="9" t="s">
         <v>616</v>
       </c>
@@ -17355,7 +17358,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="202" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A202" s="9" t="s">
         <v>619</v>
       </c>
@@ -17396,7 +17399,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="203" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A203" s="9" t="s">
         <v>623</v>
       </c>
@@ -17437,7 +17440,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="204" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A204" s="9" t="s">
         <v>626</v>
       </c>
@@ -17478,7 +17481,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="205" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A205" s="9" t="s">
         <v>630</v>
       </c>
@@ -17519,7 +17522,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="206" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A206" s="9" t="s">
         <v>633</v>
       </c>
@@ -17560,7 +17563,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="207" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A207" s="9" t="s">
         <v>637</v>
       </c>
@@ -17601,7 +17604,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="208" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A208" s="9" t="s">
         <v>640</v>
       </c>
@@ -17642,7 +17645,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="209" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A209" s="9" t="s">
         <v>644</v>
       </c>
@@ -17683,7 +17686,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="210" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A210" s="9" t="s">
         <v>648</v>
       </c>
@@ -17724,7 +17727,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="211" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A211" s="9" t="s">
         <v>652</v>
       </c>
@@ -17765,7 +17768,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="212" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A212" s="9" t="s">
         <v>655</v>
       </c>
@@ -17806,7 +17809,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="213" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A213" s="9" t="s">
         <v>659</v>
       </c>
@@ -17847,7 +17850,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="214" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A214" s="9" t="s">
         <v>663</v>
       </c>
@@ -17888,7 +17891,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="215" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A215" s="9" t="s">
         <v>667</v>
       </c>
@@ -17929,7 +17932,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="216" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A216" s="9" t="s">
         <v>670</v>
       </c>
@@ -17970,7 +17973,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="217" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A217" s="9" t="s">
         <v>674</v>
       </c>
@@ -18011,7 +18014,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="218" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="218" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A218" s="8" t="s">
         <v>123</v>
       </c>
@@ -18028,7 +18031,7 @@
       <c r="L218" s="8"/>
       <c r="M218" s="8"/>
     </row>
-    <row r="219" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A219" s="9" t="s">
         <v>678</v>
       </c>
@@ -18069,7 +18072,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="220" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A220" s="9" t="s">
         <v>682</v>
       </c>
@@ -18110,7 +18113,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="221" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A221" s="9" t="s">
         <v>686</v>
       </c>
@@ -18151,7 +18154,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="222" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A222" s="9" t="s">
         <v>690</v>
       </c>
@@ -18192,7 +18195,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="223" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A223" s="9" t="s">
         <v>694</v>
       </c>
@@ -18233,7 +18236,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="224" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A224" s="9" t="s">
         <v>698</v>
       </c>
@@ -18274,7 +18277,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="225" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A225" s="9" t="s">
         <v>702</v>
       </c>
@@ -18315,7 +18318,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="226" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A226" s="9" t="s">
         <v>706</v>
       </c>
@@ -18356,7 +18359,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="227" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A227" s="9" t="s">
         <v>710</v>
       </c>
@@ -18414,7 +18417,7 @@
       <c r="L228" s="7"/>
       <c r="M228" s="7"/>
     </row>
-    <row r="229" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="229" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A229" s="8" t="s">
         <v>22</v>
       </c>
@@ -18431,7 +18434,7 @@
       <c r="L229" s="8"/>
       <c r="M229" s="8"/>
     </row>
-    <row r="230" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A230" s="9" t="s">
         <v>715</v>
       </c>
@@ -18472,7 +18475,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="231" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A231" s="9" t="s">
         <v>717</v>
       </c>
@@ -18513,7 +18516,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="232" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A232" s="9" t="s">
         <v>719</v>
       </c>
@@ -18554,7 +18557,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="233" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A233" s="9" t="s">
         <v>721</v>
       </c>
@@ -18595,7 +18598,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="234" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A234" s="9" t="s">
         <v>723</v>
       </c>
@@ -18636,7 +18639,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="235" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A235" s="9" t="s">
         <v>725</v>
       </c>
@@ -18677,7 +18680,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="236" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A236" s="9" t="s">
         <v>727</v>
       </c>
@@ -18718,7 +18721,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="237" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A237" s="9" t="s">
         <v>729</v>
       </c>
@@ -18759,7 +18762,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="238" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A238" s="9" t="s">
         <v>731</v>
       </c>
@@ -18800,7 +18803,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="239" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A239" s="9" t="s">
         <v>734</v>
       </c>
@@ -18841,7 +18844,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="240" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A240" s="9" t="s">
         <v>736</v>
       </c>
@@ -18882,7 +18885,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="241" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A241" s="9" t="s">
         <v>740</v>
       </c>
@@ -18923,7 +18926,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="242" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A242" s="9" t="s">
         <v>743</v>
       </c>
@@ -18964,7 +18967,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="243" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A243" s="9" t="s">
         <v>745</v>
       </c>
@@ -19005,7 +19008,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="244" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A244" s="9" t="s">
         <v>747</v>
       </c>
@@ -19046,7 +19049,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="245" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A245" s="9" t="s">
         <v>749</v>
       </c>
@@ -19087,7 +19090,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="246" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A246" s="9" t="s">
         <v>751</v>
       </c>
@@ -19128,7 +19131,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="247" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A247" s="9" t="s">
         <v>755</v>
       </c>
@@ -19169,7 +19172,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="248" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A248" s="9" t="s">
         <v>758</v>
       </c>
@@ -19210,7 +19213,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="249" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A249" s="9" t="s">
         <v>760</v>
       </c>
@@ -19251,7 +19254,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="250" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A250" s="9" t="s">
         <v>762</v>
       </c>
@@ -19292,7 +19295,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="251" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A251" s="9" t="s">
         <v>764</v>
       </c>
@@ -19333,7 +19336,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="252" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A252" s="9" t="s">
         <v>766</v>
       </c>
@@ -19374,7 +19377,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="253" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A253" s="9" t="s">
         <v>768</v>
       </c>
@@ -19415,7 +19418,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="254" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A254" s="9" t="s">
         <v>770</v>
       </c>
@@ -19456,7 +19459,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="255" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A255" s="9" t="s">
         <v>774</v>
       </c>
@@ -19497,7 +19500,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="256" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A256" s="9" t="s">
         <v>777</v>
       </c>
@@ -19538,7 +19541,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="257" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A257" s="9" t="s">
         <v>781</v>
       </c>
@@ -19579,7 +19582,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="258" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A258" s="9" t="s">
         <v>784</v>
       </c>
@@ -19620,7 +19623,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="259" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A259" s="9" t="s">
         <v>786</v>
       </c>
@@ -19661,7 +19664,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="260" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="260" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A260" s="8" t="s">
         <v>123</v>
       </c>
@@ -19678,7 +19681,7 @@
       <c r="L260" s="8"/>
       <c r="M260" s="8"/>
     </row>
-    <row r="261" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A261" s="9" t="s">
         <v>788</v>
       </c>
@@ -19719,7 +19722,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="262" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A262" s="9" t="s">
         <v>792</v>
       </c>
@@ -19760,7 +19763,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="263" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A263" s="9" t="s">
         <v>796</v>
       </c>
@@ -19801,7 +19804,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="264" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A264" s="9" t="s">
         <v>800</v>
       </c>
@@ -19859,7 +19862,7 @@
       <c r="L265" s="7"/>
       <c r="M265" s="7"/>
     </row>
-    <row r="266" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="266" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A266" s="8" t="s">
         <v>22</v>
       </c>
@@ -19876,7 +19879,7 @@
       <c r="L266" s="8"/>
       <c r="M266" s="8"/>
     </row>
-    <row r="267" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A267" s="9" t="s">
         <v>805</v>
       </c>
@@ -19917,7 +19920,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="268" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A268" s="9" t="s">
         <v>807</v>
       </c>
@@ -19958,7 +19961,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="269" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A269" s="9" t="s">
         <v>809</v>
       </c>
@@ -19999,7 +20002,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="270" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A270" s="9" t="s">
         <v>811</v>
       </c>
@@ -20040,7 +20043,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="271" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A271" s="9" t="s">
         <v>813</v>
       </c>
@@ -20081,7 +20084,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="272" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A272" s="9" t="s">
         <v>815</v>
       </c>
@@ -20122,7 +20125,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="273" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A273" s="9" t="s">
         <v>817</v>
       </c>
@@ -20163,7 +20166,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="274" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A274" s="9" t="s">
         <v>821</v>
       </c>
@@ -20204,7 +20207,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="275" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A275" s="9" t="s">
         <v>824</v>
       </c>
@@ -20245,7 +20248,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="276" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A276" s="9" t="s">
         <v>828</v>
       </c>
@@ -20286,7 +20289,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="277" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A277" s="9" t="s">
         <v>831</v>
       </c>
@@ -20327,7 +20330,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="278" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A278" s="9" t="s">
         <v>833</v>
       </c>
@@ -20368,7 +20371,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="279" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A279" s="9" t="s">
         <v>835</v>
       </c>
@@ -20409,7 +20412,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="280" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A280" s="9" t="s">
         <v>839</v>
       </c>
@@ -20450,7 +20453,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="281" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A281" s="9" t="s">
         <v>842</v>
       </c>
@@ -20491,7 +20494,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="282" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A282" s="9" t="s">
         <v>846</v>
       </c>
@@ -20532,7 +20535,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="283" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A283" s="9" t="s">
         <v>849</v>
       </c>
@@ -20573,7 +20576,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="284" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A284" s="9" t="s">
         <v>853</v>
       </c>
@@ -20614,7 +20617,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="285" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A285" s="9" t="s">
         <v>856</v>
       </c>
@@ -20655,7 +20658,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="286" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A286" s="9" t="s">
         <v>860</v>
       </c>
@@ -20696,7 +20699,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="287" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A287" s="9" t="s">
         <v>863</v>
       </c>
@@ -20737,7 +20740,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="288" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A288" s="9" t="s">
         <v>867</v>
       </c>
@@ -20778,7 +20781,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="289" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="289" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A289" s="8" t="s">
         <v>123</v>
       </c>
@@ -20795,7 +20798,7 @@
       <c r="L289" s="8"/>
       <c r="M289" s="8"/>
     </row>
-    <row r="290" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A290" s="9" t="s">
         <v>870</v>
       </c>
@@ -20836,7 +20839,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="291" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A291" s="9" t="s">
         <v>874</v>
       </c>
@@ -20877,7 +20880,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="292" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A292" s="9" t="s">
         <v>878</v>
       </c>
@@ -20918,7 +20921,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="293" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A293" s="9" t="s">
         <v>882</v>
       </c>
@@ -20959,7 +20962,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="294" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A294" s="9" t="s">
         <v>886</v>
       </c>
@@ -21017,7 +21020,7 @@
       <c r="L295" s="7"/>
       <c r="M295" s="7"/>
     </row>
-    <row r="296" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="296" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A296" s="8" t="s">
         <v>22</v>
       </c>
@@ -21034,7 +21037,7 @@
       <c r="L296" s="8"/>
       <c r="M296" s="8"/>
     </row>
-    <row r="297" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A297" s="9" t="s">
         <v>891</v>
       </c>
@@ -21075,7 +21078,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="298" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A298" s="9" t="s">
         <v>893</v>
       </c>
@@ -21116,7 +21119,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="299" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A299" s="9" t="s">
         <v>895</v>
       </c>
@@ -21157,7 +21160,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="300" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A300" s="9" t="s">
         <v>897</v>
       </c>
@@ -21198,7 +21201,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="301" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A301" s="9" t="s">
         <v>899</v>
       </c>
@@ -21239,7 +21242,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="302" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A302" s="9" t="s">
         <v>901</v>
       </c>
@@ -21280,7 +21283,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="303" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A303" s="9" t="s">
         <v>903</v>
       </c>
@@ -21321,7 +21324,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="304" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A304" s="9" t="s">
         <v>905</v>
       </c>
@@ -21362,7 +21365,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="305" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A305" s="9" t="s">
         <v>907</v>
       </c>
@@ -21403,7 +21406,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="306" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A306" s="9" t="s">
         <v>911</v>
       </c>
@@ -21444,7 +21447,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="307" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A307" s="9" t="s">
         <v>914</v>
       </c>
@@ -21485,7 +21488,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="308" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A308" s="9" t="s">
         <v>918</v>
       </c>
@@ -21526,7 +21529,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="309" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A309" s="9" t="s">
         <v>921</v>
       </c>
@@ -21567,7 +21570,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="310" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A310" s="9" t="s">
         <v>925</v>
       </c>
@@ -21608,7 +21611,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="311" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A311" s="9" t="s">
         <v>928</v>
       </c>
@@ -21649,7 +21652,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="312" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A312" s="9" t="s">
         <v>932</v>
       </c>
@@ -21690,7 +21693,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="313" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A313" s="9" t="s">
         <v>935</v>
       </c>
@@ -21731,7 +21734,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="314" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A314" s="9" t="s">
         <v>939</v>
       </c>
@@ -21772,7 +21775,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="315" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="315" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A315" s="8" t="s">
         <v>123</v>
       </c>
@@ -21789,7 +21792,7 @@
       <c r="L315" s="8"/>
       <c r="M315" s="8"/>
     </row>
-    <row r="316" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A316" s="9" t="s">
         <v>942</v>
       </c>
@@ -21830,7 +21833,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="317" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A317" s="9" t="s">
         <v>946</v>
       </c>
@@ -21871,7 +21874,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="318" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A318" s="9" t="s">
         <v>950</v>
       </c>
@@ -21929,7 +21932,7 @@
       <c r="L319" s="7"/>
       <c r="M319" s="7"/>
     </row>
-    <row r="320" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="320" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A320" s="8" t="s">
         <v>22</v>
       </c>
@@ -21946,7 +21949,7 @@
       <c r="L320" s="8"/>
       <c r="M320" s="8"/>
     </row>
-    <row r="321" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A321" s="9" t="s">
         <v>955</v>
       </c>
@@ -21987,7 +21990,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="322" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A322" s="9" t="s">
         <v>957</v>
       </c>
@@ -22028,7 +22031,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="323" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A323" s="9" t="s">
         <v>959</v>
       </c>
@@ -22069,7 +22072,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="324" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A324" s="9" t="s">
         <v>961</v>
       </c>
@@ -22110,7 +22113,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="325" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A325" s="9" t="s">
         <v>963</v>
       </c>
@@ -22151,7 +22154,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="326" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A326" s="9" t="s">
         <v>965</v>
       </c>
@@ -22192,7 +22195,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="327" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A327" s="9" t="s">
         <v>967</v>
       </c>
@@ -22233,7 +22236,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="328" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A328" s="9" t="s">
         <v>971</v>
       </c>
@@ -22274,7 +22277,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="329" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A329" s="9" t="s">
         <v>974</v>
       </c>
@@ -22315,7 +22318,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="330" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A330" s="9" t="s">
         <v>978</v>
       </c>
@@ -22356,7 +22359,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="331" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A331" s="9" t="s">
         <v>981</v>
       </c>
@@ -22397,7 +22400,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="332" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A332" s="9" t="s">
         <v>985</v>
       </c>
@@ -22438,7 +22441,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="333" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A333" s="9" t="s">
         <v>988</v>
       </c>
@@ -22479,7 +22482,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="334" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A334" s="9" t="s">
         <v>992</v>
       </c>
@@ -22520,7 +22523,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="335" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A335" s="9" t="s">
         <v>995</v>
       </c>
@@ -22561,7 +22564,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="336" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A336" s="9" t="s">
         <v>997</v>
       </c>
@@ -22602,7 +22605,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="337" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A337" s="9" t="s">
         <v>999</v>
       </c>
@@ -22643,7 +22646,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="338" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A338" s="9" t="s">
         <v>1003</v>
       </c>
@@ -22684,7 +22687,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="339" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A339" s="9" t="s">
         <v>1006</v>
       </c>
@@ -22725,7 +22728,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="340" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A340" s="9" t="s">
         <v>1010</v>
       </c>
@@ -22766,7 +22769,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="341" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A341" s="9" t="s">
         <v>1013</v>
       </c>
@@ -22807,7 +22810,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="342" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A342" s="9" t="s">
         <v>1017</v>
       </c>
@@ -22848,7 +22851,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="343" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A343" s="9" t="s">
         <v>1020</v>
       </c>
@@ -22889,7 +22892,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="344" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A344" s="9" t="s">
         <v>1024</v>
       </c>
@@ -22930,7 +22933,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="345" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="345" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A345" s="8" t="s">
         <v>123</v>
       </c>
@@ -22947,7 +22950,7 @@
       <c r="L345" s="8"/>
       <c r="M345" s="8"/>
     </row>
-    <row r="346" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A346" s="9" t="s">
         <v>1027</v>
       </c>
@@ -22988,7 +22991,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="347" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A347" s="9" t="s">
         <v>1031</v>
       </c>
@@ -23029,7 +23032,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="348" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A348" s="9" t="s">
         <v>1035</v>
       </c>
@@ -23087,7 +23090,7 @@
       <c r="L349" s="7"/>
       <c r="M349" s="7"/>
     </row>
-    <row r="350" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="350" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A350" s="8" t="s">
         <v>22</v>
       </c>
@@ -23104,7 +23107,7 @@
       <c r="L350" s="8"/>
       <c r="M350" s="8"/>
     </row>
-    <row r="351" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A351" s="9" t="s">
         <v>1040</v>
       </c>
@@ -23145,7 +23148,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="352" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A352" s="9" t="s">
         <v>1042</v>
       </c>
@@ -23186,7 +23189,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="353" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A353" s="9" t="s">
         <v>1044</v>
       </c>
@@ -23227,7 +23230,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="354" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A354" s="9" t="s">
         <v>1046</v>
       </c>
@@ -23268,7 +23271,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="355" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A355" s="9" t="s">
         <v>1048</v>
       </c>
@@ -23309,7 +23312,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="356" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A356" s="9" t="s">
         <v>1050</v>
       </c>
@@ -23350,7 +23353,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="357" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A357" s="9" t="s">
         <v>1052</v>
       </c>
@@ -23391,7 +23394,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="358" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A358" s="9" t="s">
         <v>1056</v>
       </c>
@@ -23432,7 +23435,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="359" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A359" s="9" t="s">
         <v>1059</v>
       </c>
@@ -23473,7 +23476,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="360" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A360" s="9" t="s">
         <v>1063</v>
       </c>
@@ -23514,7 +23517,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="361" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A361" s="9" t="s">
         <v>1066</v>
       </c>
@@ -23555,7 +23558,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="362" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A362" s="9" t="s">
         <v>1068</v>
       </c>
@@ -23596,7 +23599,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="363" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A363" s="9" t="s">
         <v>1070</v>
       </c>
@@ -23637,7 +23640,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="364" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A364" s="9" t="s">
         <v>1074</v>
       </c>
@@ -23678,7 +23681,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="365" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A365" s="9" t="s">
         <v>1077</v>
       </c>
@@ -23719,7 +23722,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="366" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A366" s="9" t="s">
         <v>1079</v>
       </c>
@@ -23760,7 +23763,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="367" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A367" s="9" t="s">
         <v>1081</v>
       </c>
@@ -23801,7 +23804,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="368" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A368" s="9" t="s">
         <v>1085</v>
       </c>
@@ -23842,7 +23845,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="369" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A369" s="9" t="s">
         <v>1088</v>
       </c>
@@ -23883,7 +23886,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="370" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A370" s="9" t="s">
         <v>1092</v>
       </c>
@@ -23924,7 +23927,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="371" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="371" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A371" s="8" t="s">
         <v>123</v>
       </c>
@@ -23941,7 +23944,7 @@
       <c r="L371" s="8"/>
       <c r="M371" s="8"/>
     </row>
-    <row r="372" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A372" s="9" t="s">
         <v>1095</v>
       </c>
@@ -23982,7 +23985,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="373" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A373" s="9" t="s">
         <v>1099</v>
       </c>
@@ -24023,7 +24026,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="374" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A374" s="9" t="s">
         <v>1103</v>
       </c>
@@ -24081,7 +24084,7 @@
       <c r="L375" s="7"/>
       <c r="M375" s="7"/>
     </row>
-    <row r="376" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="376" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A376" s="8" t="s">
         <v>22</v>
       </c>
@@ -24098,7 +24101,7 @@
       <c r="L376" s="8"/>
       <c r="M376" s="8"/>
     </row>
-    <row r="377" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A377" s="9" t="s">
         <v>1108</v>
       </c>
@@ -24139,7 +24142,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="378" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A378" s="9" t="s">
         <v>1110</v>
       </c>
@@ -24180,7 +24183,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="379" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A379" s="9" t="s">
         <v>1112</v>
       </c>
@@ -24221,7 +24224,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="380" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A380" s="9" t="s">
         <v>1114</v>
       </c>
@@ -24262,7 +24265,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="381" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A381" s="9" t="s">
         <v>1116</v>
       </c>
@@ -24303,7 +24306,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="382" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A382" s="9" t="s">
         <v>1118</v>
       </c>
@@ -24344,7 +24347,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="383" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A383" s="9" t="s">
         <v>1120</v>
       </c>
@@ -24385,7 +24388,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="384" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A384" s="9" t="s">
         <v>1124</v>
       </c>
@@ -24426,7 +24429,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="385" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A385" s="9" t="s">
         <v>1127</v>
       </c>
@@ -24467,7 +24470,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="386" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A386" s="9" t="s">
         <v>1131</v>
       </c>
@@ -24508,7 +24511,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="387" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="387" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A387" s="8" t="s">
         <v>123</v>
       </c>
@@ -24525,7 +24528,7 @@
       <c r="L387" s="8"/>
       <c r="M387" s="8"/>
     </row>
-    <row r="388" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A388" s="9" t="s">
         <v>1134</v>
       </c>
@@ -24566,7 +24569,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="389" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A389" s="9" t="s">
         <v>1138</v>
       </c>
@@ -24624,7 +24627,7 @@
       <c r="L390" s="7"/>
       <c r="M390" s="7"/>
     </row>
-    <row r="391" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="391" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A391" s="8" t="s">
         <v>22</v>
       </c>
@@ -24641,7 +24644,7 @@
       <c r="L391" s="8"/>
       <c r="M391" s="8"/>
     </row>
-    <row r="392" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A392" s="9" t="s">
         <v>1143</v>
       </c>
@@ -24682,7 +24685,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="393" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A393" s="9" t="s">
         <v>1145</v>
       </c>
@@ -24723,7 +24726,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="394" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A394" s="9" t="s">
         <v>1147</v>
       </c>
@@ -24764,7 +24767,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="395" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A395" s="9" t="s">
         <v>1149</v>
       </c>
@@ -24805,7 +24808,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="396" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A396" s="9" t="s">
         <v>1151</v>
       </c>
@@ -24846,7 +24849,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="397" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A397" s="9" t="s">
         <v>1153</v>
       </c>
@@ -24887,7 +24890,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="398" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A398" s="9" t="s">
         <v>1155</v>
       </c>
@@ -24928,7 +24931,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="399" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A399" s="9" t="s">
         <v>1159</v>
       </c>
@@ -24969,7 +24972,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="400" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A400" s="9" t="s">
         <v>1162</v>
       </c>
@@ -25010,7 +25013,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="401" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A401" s="9" t="s">
         <v>1164</v>
       </c>
@@ -25051,7 +25054,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="402" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A402" s="9" t="s">
         <v>1166</v>
       </c>
@@ -25092,7 +25095,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="403" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A403" s="9" t="s">
         <v>1170</v>
       </c>
@@ -25133,7 +25136,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="404" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A404" s="9" t="s">
         <v>1173</v>
       </c>
@@ -25174,7 +25177,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="405" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A405" s="9" t="s">
         <v>1175</v>
       </c>
@@ -25215,7 +25218,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="406" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A406" s="9" t="s">
         <v>1177</v>
       </c>
@@ -25256,7 +25259,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="407" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A407" s="9" t="s">
         <v>1181</v>
       </c>
@@ -25297,7 +25300,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="408" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A408" s="9" t="s">
         <v>1184</v>
       </c>
@@ -25338,7 +25341,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="409" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A409" s="9" t="s">
         <v>1188</v>
       </c>
@@ -25379,7 +25382,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="410" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="410" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A410" s="8" t="s">
         <v>123</v>
       </c>
@@ -25396,7 +25399,7 @@
       <c r="L410" s="8"/>
       <c r="M410" s="8"/>
     </row>
-    <row r="411" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A411" s="9" t="s">
         <v>1191</v>
       </c>
@@ -25437,7 +25440,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="412" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A412" s="9" t="s">
         <v>1195</v>
       </c>
@@ -25495,7 +25498,7 @@
       <c r="L413" s="7"/>
       <c r="M413" s="7"/>
     </row>
-    <row r="414" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="414" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A414" s="8" t="s">
         <v>22</v>
       </c>
@@ -25512,7 +25515,7 @@
       <c r="L414" s="8"/>
       <c r="M414" s="8"/>
     </row>
-    <row r="415" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A415" s="9" t="s">
         <v>1200</v>
       </c>
@@ -25553,7 +25556,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="416" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A416" s="9" t="s">
         <v>1202</v>
       </c>
@@ -25594,7 +25597,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="417" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A417" s="9" t="s">
         <v>1204</v>
       </c>
@@ -25635,7 +25638,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="418" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A418" s="9" t="s">
         <v>1206</v>
       </c>
@@ -25676,7 +25679,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="419" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A419" s="9" t="s">
         <v>1208</v>
       </c>
@@ -25717,7 +25720,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="420" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A420" s="9" t="s">
         <v>1210</v>
       </c>
@@ -25758,7 +25761,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="421" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A421" s="9" t="s">
         <v>1212</v>
       </c>
@@ -25799,7 +25802,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="422" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A422" s="9" t="s">
         <v>1216</v>
       </c>
@@ -25840,7 +25843,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="423" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A423" s="9" t="s">
         <v>1219</v>
       </c>
@@ -25881,7 +25884,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="424" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A424" s="9" t="s">
         <v>1223</v>
       </c>
@@ -25922,7 +25925,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="425" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A425" s="9" t="s">
         <v>1226</v>
       </c>
@@ -25963,7 +25966,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="426" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A426" s="9" t="s">
         <v>1230</v>
       </c>
@@ -26004,7 +26007,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="427" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A427" s="9" t="s">
         <v>1233</v>
       </c>
@@ -26045,7 +26048,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="428" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A428" s="9" t="s">
         <v>1237</v>
       </c>
@@ -26086,7 +26089,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="429" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A429" s="9" t="s">
         <v>1240</v>
       </c>
@@ -26127,7 +26130,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="430" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A430" s="9" t="s">
         <v>1244</v>
       </c>
@@ -26168,7 +26171,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="431" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="431" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A431" s="8" t="s">
         <v>123</v>
       </c>
@@ -26185,7 +26188,7 @@
       <c r="L431" s="8"/>
       <c r="M431" s="8"/>
     </row>
-    <row r="432" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A432" s="9" t="s">
         <v>1247</v>
       </c>
@@ -26226,7 +26229,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="433" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A433" s="9" t="s">
         <v>1251</v>
       </c>
@@ -26284,7 +26287,7 @@
       <c r="L434" s="7"/>
       <c r="M434" s="7"/>
     </row>
-    <row r="435" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="435" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A435" s="8" t="s">
         <v>22</v>
       </c>
@@ -26301,7 +26304,7 @@
       <c r="L435" s="8"/>
       <c r="M435" s="8"/>
     </row>
-    <row r="436" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A436" s="9" t="s">
         <v>1256</v>
       </c>
@@ -26342,7 +26345,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="437" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A437" s="9" t="s">
         <v>1258</v>
       </c>
@@ -26383,7 +26386,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="438" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A438" s="9" t="s">
         <v>1260</v>
       </c>
@@ -26424,7 +26427,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="439" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A439" s="9" t="s">
         <v>1262</v>
       </c>
@@ -26465,7 +26468,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="440" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A440" s="9" t="s">
         <v>1264</v>
       </c>
@@ -26506,7 +26509,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="441" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A441" s="9" t="s">
         <v>1266</v>
       </c>
@@ -26547,7 +26550,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="442" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A442" s="9" t="s">
         <v>1268</v>
       </c>
@@ -26588,7 +26591,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="443" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A443" s="9" t="s">
         <v>1272</v>
       </c>
@@ -26629,7 +26632,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="444" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A444" s="9" t="s">
         <v>1275</v>
       </c>
@@ -26670,7 +26673,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="445" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A445" s="9" t="s">
         <v>1279</v>
       </c>
@@ -26711,7 +26714,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="446" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="446" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A446" s="8" t="s">
         <v>123</v>
       </c>
@@ -26728,7 +26731,7 @@
       <c r="L446" s="8"/>
       <c r="M446" s="8"/>
     </row>
-    <row r="447" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A447" s="9" t="s">
         <v>1282</v>
       </c>
@@ -26769,7 +26772,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="448" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A448" s="9" t="s">
         <v>1286</v>
       </c>
@@ -26827,7 +26830,7 @@
       <c r="L449" s="7"/>
       <c r="M449" s="7"/>
     </row>
-    <row r="450" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="450" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A450" s="8" t="s">
         <v>22</v>
       </c>
@@ -26844,7 +26847,7 @@
       <c r="L450" s="8"/>
       <c r="M450" s="8"/>
     </row>
-    <row r="451" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A451" s="9" t="s">
         <v>1291</v>
       </c>
@@ -26885,7 +26888,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="452" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A452" s="9" t="s">
         <v>1293</v>
       </c>
@@ -26926,7 +26929,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="453" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A453" s="9" t="s">
         <v>1295</v>
       </c>
@@ -26967,7 +26970,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="454" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A454" s="9" t="s">
         <v>1297</v>
       </c>
@@ -27008,7 +27011,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="455" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A455" s="9" t="s">
         <v>1299</v>
       </c>
@@ -27049,7 +27052,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="456" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A456" s="9" t="s">
         <v>1301</v>
       </c>
@@ -27090,7 +27093,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="457" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A457" s="9" t="s">
         <v>1303</v>
       </c>
@@ -27131,7 +27134,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="458" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A458" s="9" t="s">
         <v>1305</v>
       </c>
@@ -27172,7 +27175,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="459" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A459" s="9" t="s">
         <v>1307</v>
       </c>
@@ -27213,7 +27216,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="460" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A460" s="9" t="s">
         <v>1309</v>
       </c>
@@ -27254,7 +27257,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="461" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="461" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A461" s="8" t="s">
         <v>123</v>
       </c>
@@ -27271,7 +27274,7 @@
       <c r="L461" s="8"/>
       <c r="M461" s="8"/>
     </row>
-    <row r="462" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A462" s="9" t="s">
         <v>1311</v>
       </c>
@@ -27329,7 +27332,7 @@
       <c r="L463" s="7"/>
       <c r="M463" s="7"/>
     </row>
-    <row r="464" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="464" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A464" s="8" t="s">
         <v>22</v>
       </c>
@@ -27346,7 +27349,7 @@
       <c r="L464" s="8"/>
       <c r="M464" s="8"/>
     </row>
-    <row r="465" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A465" s="9" t="s">
         <v>1316</v>
       </c>
@@ -27387,7 +27390,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="466" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A466" s="9" t="s">
         <v>1318</v>
       </c>
@@ -27428,7 +27431,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="467" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A467" s="9" t="s">
         <v>1320</v>
       </c>
@@ -27469,7 +27472,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="468" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A468" s="9" t="s">
         <v>1322</v>
       </c>
@@ -27510,7 +27513,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="469" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A469" s="9" t="s">
         <v>1324</v>
       </c>
@@ -27551,7 +27554,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="470" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A470" s="9" t="s">
         <v>1326</v>
       </c>
@@ -27592,7 +27595,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="471" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A471" s="9" t="s">
         <v>1328</v>
       </c>
@@ -27633,7 +27636,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="472" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A472" s="9" t="s">
         <v>1330</v>
       </c>
@@ -27674,7 +27677,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="473" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A473" s="9" t="s">
         <v>1332</v>
       </c>
@@ -27715,7 +27718,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="474" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A474" s="9" t="s">
         <v>1334</v>
       </c>
@@ -27756,7 +27759,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="475" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="475" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A475" s="8" t="s">
         <v>123</v>
       </c>
@@ -27773,7 +27776,7 @@
       <c r="L475" s="8"/>
       <c r="M475" s="8"/>
     </row>
-    <row r="476" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A476" s="9" t="s">
         <v>1336</v>
       </c>
@@ -27831,7 +27834,7 @@
       <c r="L477" s="7"/>
       <c r="M477" s="7"/>
     </row>
-    <row r="478" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="478" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A478" s="8" t="s">
         <v>22</v>
       </c>
@@ -27848,7 +27851,7 @@
       <c r="L478" s="8"/>
       <c r="M478" s="8"/>
     </row>
-    <row r="479" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A479" s="9" t="s">
         <v>1341</v>
       </c>
@@ -27889,7 +27892,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="480" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A480" s="9" t="s">
         <v>1343</v>
       </c>
@@ -27930,7 +27933,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="481" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A481" s="9" t="s">
         <v>1345</v>
       </c>
@@ -27971,7 +27974,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="482" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A482" s="9" t="s">
         <v>1347</v>
       </c>
@@ -28012,7 +28015,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="483" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A483" s="9" t="s">
         <v>1349</v>
       </c>
@@ -28053,7 +28056,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="484" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A484" s="9" t="s">
         <v>1351</v>
       </c>
@@ -28094,7 +28097,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="485" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="485" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A485" s="8" t="s">
         <v>123</v>
       </c>
@@ -28111,7 +28114,7 @@
       <c r="L485" s="8"/>
       <c r="M485" s="8"/>
     </row>
-    <row r="486" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A486" s="9" t="s">
         <v>1353</v>
       </c>
@@ -28169,7 +28172,7 @@
       <c r="L487" s="7"/>
       <c r="M487" s="7"/>
     </row>
-    <row r="488" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="488" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A488" s="8" t="s">
         <v>22</v>
       </c>
@@ -28186,7 +28189,7 @@
       <c r="L488" s="8"/>
       <c r="M488" s="8"/>
     </row>
-    <row r="489" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A489" s="9" t="s">
         <v>1358</v>
       </c>
@@ -28227,7 +28230,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="490" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A490" s="9" t="s">
         <v>1360</v>
       </c>
@@ -28268,7 +28271,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="491" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A491" s="9" t="s">
         <v>1362</v>
       </c>
@@ -28309,7 +28312,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="492" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A492" s="9" t="s">
         <v>1364</v>
       </c>
@@ -28350,7 +28353,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="493" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A493" s="9" t="s">
         <v>1366</v>
       </c>
@@ -28391,7 +28394,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="494" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A494" s="9" t="s">
         <v>1368</v>
       </c>
@@ -28432,7 +28435,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="495" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A495" s="9" t="s">
         <v>1370</v>
       </c>
@@ -28473,7 +28476,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="496" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A496" s="9" t="s">
         <v>1374</v>
       </c>
@@ -28514,7 +28517,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="497" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A497" s="9" t="s">
         <v>1377</v>
       </c>
@@ -28555,7 +28558,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="498" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A498" s="9" t="s">
         <v>1381</v>
       </c>
@@ -28596,7 +28599,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="499" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A499" s="9" t="s">
         <v>1384</v>
       </c>
@@ -28637,7 +28640,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="500" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A500" s="9" t="s">
         <v>1388</v>
       </c>
@@ -28678,7 +28681,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="501" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A501" s="9" t="s">
         <v>1391</v>
       </c>
@@ -28719,7 +28722,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="502" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A502" s="9" t="s">
         <v>1395</v>
       </c>
@@ -28760,7 +28763,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="503" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A503" s="9" t="s">
         <v>1398</v>
       </c>
@@ -28801,7 +28804,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="504" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A504" s="9" t="s">
         <v>1402</v>
       </c>
@@ -28842,7 +28845,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="505" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A505" s="9" t="s">
         <v>1405</v>
       </c>
@@ -28883,7 +28886,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="506" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A506" s="9" t="s">
         <v>1409</v>
       </c>
@@ -28924,7 +28927,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="507" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A507" s="9" t="s">
         <v>1412</v>
       </c>
@@ -28965,7 +28968,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="508" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A508" s="9" t="s">
         <v>1416</v>
       </c>
@@ -29006,7 +29009,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="509" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A509" s="9" t="s">
         <v>1419</v>
       </c>
@@ -29047,7 +29050,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="510" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A510" s="9" t="s">
         <v>1423</v>
       </c>
@@ -29088,7 +29091,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="511" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="511" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A511" s="8" t="s">
         <v>123</v>
       </c>
@@ -29105,7 +29108,7 @@
       <c r="L511" s="8"/>
       <c r="M511" s="8"/>
     </row>
-    <row r="512" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A512" s="9" t="s">
         <v>1426</v>
       </c>
@@ -29146,7 +29149,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="513" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A513" s="9" t="s">
         <v>1430</v>
       </c>
@@ -29204,7 +29207,7 @@
       <c r="L514" s="7"/>
       <c r="M514" s="7"/>
     </row>
-    <row r="515" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="515" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A515" s="8" t="s">
         <v>22</v>
       </c>
@@ -29221,7 +29224,7 @@
       <c r="L515" s="8"/>
       <c r="M515" s="8"/>
     </row>
-    <row r="516" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A516" s="9" t="s">
         <v>1435</v>
       </c>
@@ -29262,7 +29265,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="517" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A517" s="9" t="s">
         <v>1437</v>
       </c>
@@ -29303,7 +29306,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="518" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A518" s="9" t="s">
         <v>1439</v>
       </c>
@@ -29344,7 +29347,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="519" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A519" s="9" t="s">
         <v>1441</v>
       </c>
@@ -29385,7 +29388,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="520" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A520" s="9" t="s">
         <v>1443</v>
       </c>
@@ -29426,7 +29429,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="521" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A521" s="9" t="s">
         <v>1445</v>
       </c>
@@ -29467,7 +29470,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="522" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A522" s="9" t="s">
         <v>1447</v>
       </c>
@@ -29508,7 +29511,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="523" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A523" s="9" t="s">
         <v>1451</v>
       </c>
@@ -29549,7 +29552,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="524" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A524" s="9" t="s">
         <v>1454</v>
       </c>
@@ -29590,7 +29593,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="525" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A525" s="9" t="s">
         <v>1458</v>
       </c>
@@ -29631,7 +29634,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="526" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A526" s="9" t="s">
         <v>1462</v>
       </c>
@@ -29672,7 +29675,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="527" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A527" s="9" t="s">
         <v>1466</v>
       </c>
@@ -29713,7 +29716,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="528" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A528" s="9" t="s">
         <v>1469</v>
       </c>
@@ -29754,7 +29757,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="529" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A529" s="9" t="s">
         <v>1473</v>
       </c>
@@ -29795,7 +29798,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="530" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="530" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A530" s="8" t="s">
         <v>123</v>
       </c>
@@ -29812,7 +29815,7 @@
       <c r="L530" s="8"/>
       <c r="M530" s="8"/>
     </row>
-    <row r="531" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A531" s="9" t="s">
         <v>1476</v>
       </c>
@@ -29853,7 +29856,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="532" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A532" s="9" t="s">
         <v>1480</v>
       </c>
@@ -29894,7 +29897,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="533" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A533" s="9" t="s">
         <v>1484</v>
       </c>
@@ -29935,7 +29938,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="534" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A534" s="9" t="s">
         <v>1488</v>
       </c>
@@ -29976,7 +29979,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="535" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A535" s="9" t="s">
         <v>1492</v>
       </c>
@@ -30017,7 +30020,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="536" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A536" s="9" t="s">
         <v>1496</v>
       </c>
@@ -30058,7 +30061,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="537" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A537" s="9" t="s">
         <v>1500</v>
       </c>
@@ -30116,7 +30119,7 @@
       <c r="L538" s="7"/>
       <c r="M538" s="7"/>
     </row>
-    <row r="539" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="539" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A539" s="8" t="s">
         <v>22</v>
       </c>
@@ -30133,7 +30136,7 @@
       <c r="L539" s="8"/>
       <c r="M539" s="8"/>
     </row>
-    <row r="540" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A540" s="9" t="s">
         <v>1505</v>
       </c>
@@ -30174,7 +30177,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="541" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A541" s="9" t="s">
         <v>1507</v>
       </c>
@@ -30215,7 +30218,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="542" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A542" s="9" t="s">
         <v>1509</v>
       </c>
@@ -30256,7 +30259,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="543" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A543" s="9" t="s">
         <v>1511</v>
       </c>
@@ -30297,7 +30300,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="544" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A544" s="9" t="s">
         <v>1513</v>
       </c>
@@ -30338,7 +30341,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="545" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A545" s="9" t="s">
         <v>1515</v>
       </c>
@@ -30379,7 +30382,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="546" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A546" s="9" t="s">
         <v>1517</v>
       </c>
@@ -30420,7 +30423,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="547" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A547" s="9" t="s">
         <v>1521</v>
       </c>
@@ -30461,7 +30464,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="548" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A548" s="9" t="s">
         <v>1524</v>
       </c>
@@ -30502,7 +30505,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="549" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A549" s="9" t="s">
         <v>1528</v>
       </c>
@@ -30543,7 +30546,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="550" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A550" s="9" t="s">
         <v>1531</v>
       </c>
@@ -30584,7 +30587,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="551" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A551" s="9" t="s">
         <v>1535</v>
       </c>
@@ -30625,7 +30628,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="552" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A552" s="9" t="s">
         <v>1538</v>
       </c>
@@ -30666,7 +30669,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="553" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A553" s="9" t="s">
         <v>1542</v>
       </c>
@@ -30707,7 +30710,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="554" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A554" s="9" t="s">
         <v>1545</v>
       </c>
@@ -30748,7 +30751,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="555" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A555" s="9" t="s">
         <v>1549</v>
       </c>
@@ -30789,7 +30792,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="556" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A556" s="9" t="s">
         <v>1552</v>
       </c>
@@ -30830,7 +30833,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="557" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A557" s="9" t="s">
         <v>1556</v>
       </c>
@@ -30871,7 +30874,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="558" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="558" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A558" s="8" t="s">
         <v>123</v>
       </c>
@@ -30888,7 +30891,7 @@
       <c r="L558" s="8"/>
       <c r="M558" s="8"/>
     </row>
-    <row r="559" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A559" s="9" t="s">
         <v>1559</v>
       </c>
@@ -30929,7 +30932,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="560" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A560" s="9" t="s">
         <v>1563</v>
       </c>
@@ -30970,7 +30973,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="561" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A561" s="9" t="s">
         <v>1567</v>
       </c>
@@ -31011,7 +31014,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="562" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A562" s="9" t="s">
         <v>1571</v>
       </c>
@@ -31052,7 +31055,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="563" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A563" s="9" t="s">
         <v>1575</v>
       </c>
@@ -31093,7 +31096,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="564" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A564" s="9" t="s">
         <v>1579</v>
       </c>
@@ -31134,7 +31137,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="565" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A565" s="9" t="s">
         <v>1583</v>
       </c>
@@ -31192,7 +31195,7 @@
       <c r="L566" s="7"/>
       <c r="M566" s="7"/>
     </row>
-    <row r="567" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="567" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A567" s="8" t="s">
         <v>22</v>
       </c>
@@ -31209,7 +31212,7 @@
       <c r="L567" s="8"/>
       <c r="M567" s="8"/>
     </row>
-    <row r="568" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A568" s="9" t="s">
         <v>1588</v>
       </c>
@@ -31250,7 +31253,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="569" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A569" s="9" t="s">
         <v>1590</v>
       </c>
@@ -31291,7 +31294,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="570" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A570" s="9" t="s">
         <v>1592</v>
       </c>
@@ -31332,7 +31335,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="571" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A571" s="9" t="s">
         <v>1594</v>
       </c>
@@ -31373,7 +31376,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="572" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A572" s="9" t="s">
         <v>1596</v>
       </c>
@@ -31414,7 +31417,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="573" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A573" s="9" t="s">
         <v>1598</v>
       </c>
@@ -31455,7 +31458,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="574" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A574" s="9" t="s">
         <v>1600</v>
       </c>
@@ -31496,7 +31499,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="575" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A575" s="9" t="s">
         <v>1603</v>
       </c>
@@ -31537,7 +31540,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="576" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A576" s="9" t="s">
         <v>1605</v>
       </c>
@@ -31578,7 +31581,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="577" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A577" s="9" t="s">
         <v>1609</v>
       </c>
@@ -31619,7 +31622,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="578" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A578" s="9" t="s">
         <v>1612</v>
       </c>
@@ -31660,7 +31663,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="579" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A579" s="9" t="s">
         <v>1616</v>
       </c>
@@ -31701,7 +31704,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="580" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A580" s="9" t="s">
         <v>1619</v>
       </c>
@@ -31742,7 +31745,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="581" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A581" s="9" t="s">
         <v>1622</v>
       </c>
@@ -31783,7 +31786,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="582" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A582" s="9" t="s">
         <v>1624</v>
       </c>
@@ -31824,7 +31827,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="583" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A583" s="9" t="s">
         <v>1628</v>
       </c>
@@ -31865,7 +31868,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="584" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A584" s="9" t="s">
         <v>1631</v>
       </c>
@@ -31906,7 +31909,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="585" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A585" s="9" t="s">
         <v>1635</v>
       </c>
@@ -31947,7 +31950,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="586" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A586" s="9" t="s">
         <v>1638</v>
       </c>
@@ -31988,7 +31991,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="587" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A587" s="9" t="s">
         <v>1642</v>
       </c>
@@ -32029,7 +32032,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="588" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A588" s="9" t="s">
         <v>1645</v>
       </c>
@@ -32070,7 +32073,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="589" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A589" s="9" t="s">
         <v>1649</v>
       </c>
@@ -32111,7 +32114,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="590" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A590" s="9" t="s">
         <v>1652</v>
       </c>
@@ -32152,7 +32155,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="591" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A591" s="9" t="s">
         <v>1656</v>
       </c>
@@ -32193,7 +32196,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="592" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A592" s="9" t="s">
         <v>1659</v>
       </c>
@@ -32234,7 +32237,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="593" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A593" s="9" t="s">
         <v>1662</v>
       </c>
@@ -32275,7 +32278,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="594" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="594" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A594" s="8" t="s">
         <v>123</v>
       </c>
@@ -32292,7 +32295,7 @@
       <c r="L594" s="8"/>
       <c r="M594" s="8"/>
     </row>
-    <row r="595" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A595" s="9" t="s">
         <v>1664</v>
       </c>
@@ -32333,7 +32336,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="596" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A596" s="9" t="s">
         <v>1668</v>
       </c>
@@ -32374,7 +32377,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="597" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A597" s="9" t="s">
         <v>1672</v>
       </c>
@@ -32415,7 +32418,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="598" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A598" s="9" t="s">
         <v>1676</v>
       </c>
@@ -32456,7 +32459,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="599" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A599" s="9" t="s">
         <v>1680</v>
       </c>
@@ -32497,7 +32500,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="600" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A600" s="9" t="s">
         <v>1684</v>
       </c>
@@ -32538,7 +32541,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="601" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A601" s="9" t="s">
         <v>1688</v>
       </c>
@@ -32579,7 +32582,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="602" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A602" s="9" t="s">
         <v>1692</v>
       </c>
@@ -32637,7 +32640,7 @@
       <c r="L603" s="7"/>
       <c r="M603" s="7"/>
     </row>
-    <row r="604" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="604" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A604" s="8" t="s">
         <v>22</v>
       </c>
@@ -32654,7 +32657,7 @@
       <c r="L604" s="8"/>
       <c r="M604" s="8"/>
     </row>
-    <row r="605" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A605" s="9" t="s">
         <v>1697</v>
       </c>
@@ -32695,7 +32698,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="606" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A606" s="9" t="s">
         <v>1699</v>
       </c>
@@ -32736,7 +32739,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="607" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A607" s="9" t="s">
         <v>1701</v>
       </c>
@@ -32777,7 +32780,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="608" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A608" s="9" t="s">
         <v>1703</v>
       </c>
@@ -32818,7 +32821,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="609" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A609" s="9" t="s">
         <v>1705</v>
       </c>
@@ -32859,7 +32862,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="610" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A610" s="9" t="s">
         <v>1707</v>
       </c>
@@ -32900,7 +32903,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="611" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A611" s="9" t="s">
         <v>1709</v>
       </c>
@@ -32941,7 +32944,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="612" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A612" s="9" t="s">
         <v>1712</v>
       </c>
@@ -32982,7 +32985,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="613" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A613" s="9" t="s">
         <v>1714</v>
       </c>
@@ -33023,7 +33026,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="614" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A614" s="9" t="s">
         <v>1716</v>
       </c>
@@ -33064,7 +33067,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="615" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A615" s="9" t="s">
         <v>1718</v>
       </c>
@@ -33105,7 +33108,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="616" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A616" s="9" t="s">
         <v>1720</v>
       </c>
@@ -33146,7 +33149,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="617" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A617" s="9" t="s">
         <v>1722</v>
       </c>
@@ -33187,7 +33190,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="618" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A618" s="9" t="s">
         <v>1724</v>
       </c>
@@ -33228,7 +33231,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="619" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A619" s="9" t="s">
         <v>1726</v>
       </c>
@@ -33269,7 +33272,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="620" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A620" s="9" t="s">
         <v>1728</v>
       </c>
@@ -33310,7 +33313,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="621" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A621" s="9" t="s">
         <v>1730</v>
       </c>
@@ -33351,7 +33354,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="622" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A622" s="9" t="s">
         <v>1733</v>
       </c>
@@ -33392,7 +33395,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="623" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A623" s="9" t="s">
         <v>1735</v>
       </c>
@@ -33433,7 +33436,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="624" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A624" s="9" t="s">
         <v>1737</v>
       </c>
@@ -33474,7 +33477,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="625" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A625" s="9" t="s">
         <v>1739</v>
       </c>
@@ -33515,7 +33518,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="626" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A626" s="9" t="s">
         <v>1741</v>
       </c>
@@ -33556,7 +33559,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="627" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A627" s="9" t="s">
         <v>1743</v>
       </c>
@@ -33597,7 +33600,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="628" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A628" s="9" t="s">
         <v>1746</v>
       </c>
@@ -33638,7 +33641,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="629" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A629" s="9" t="s">
         <v>1748</v>
       </c>
@@ -33679,7 +33682,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="630" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A630" s="9" t="s">
         <v>1750</v>
       </c>
@@ -33720,7 +33723,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="631" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="631" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A631" s="8" t="s">
         <v>123</v>
       </c>
@@ -33737,7 +33740,7 @@
       <c r="L631" s="8"/>
       <c r="M631" s="8"/>
     </row>
-    <row r="632" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A632" s="9" t="s">
         <v>1752</v>
       </c>
@@ -33778,7 +33781,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="633" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A633" s="9" t="s">
         <v>1756</v>
       </c>
@@ -33819,7 +33822,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="634" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A634" s="9" t="s">
         <v>1758</v>
       </c>
@@ -33860,7 +33863,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="635" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A635" s="9" t="s">
         <v>1761</v>
       </c>
@@ -33901,7 +33904,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="636" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A636" s="9" t="s">
         <v>1764</v>
       </c>
@@ -33942,7 +33945,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="637" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A637" s="9" t="s">
         <v>1766</v>
       </c>
@@ -34072,6 +34075,9 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
   <dimension ref="A1:M212"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
@@ -34225,7 +34231,7 @@
       <c r="L12" s="7"/>
       <c r="M12" s="7"/>
     </row>
-    <row r="13" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A13" s="8" t="s">
         <v>22</v>
       </c>
@@ -34242,7 +34248,7 @@
       <c r="L13" s="8"/>
       <c r="M13" s="8"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A14" s="9" t="s">
         <v>1771</v>
       </c>
@@ -34283,7 +34289,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A15" s="9" t="s">
         <v>1773</v>
       </c>
@@ -34324,7 +34330,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A16" s="9" t="s">
         <v>1775</v>
       </c>
@@ -34365,7 +34371,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A17" s="9" t="s">
         <v>1777</v>
       </c>
@@ -34406,7 +34412,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A18" s="9" t="s">
         <v>1779</v>
       </c>
@@ -34447,7 +34453,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A19" s="9" t="s">
         <v>1781</v>
       </c>
@@ -34488,7 +34494,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A20" s="9" t="s">
         <v>1783</v>
       </c>
@@ -34529,7 +34535,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A21" s="9" t="s">
         <v>1787</v>
       </c>
@@ -34570,7 +34576,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A22" s="8" t="s">
         <v>123</v>
       </c>
@@ -34587,7 +34593,7 @@
       <c r="L22" s="8"/>
       <c r="M22" s="8"/>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A23" s="9" t="s">
         <v>1791</v>
       </c>
@@ -34628,7 +34634,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A24" s="9" t="s">
         <v>1795</v>
       </c>
@@ -34669,7 +34675,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A25" s="9" t="s">
         <v>1799</v>
       </c>
@@ -34710,7 +34716,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A26" s="9" t="s">
         <v>1803</v>
       </c>
@@ -34768,7 +34774,7 @@
       <c r="L27" s="7"/>
       <c r="M27" s="7"/>
     </row>
-    <row r="28" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A28" s="8" t="s">
         <v>22</v>
       </c>
@@ -34785,7 +34791,7 @@
       <c r="L28" s="8"/>
       <c r="M28" s="8"/>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A29" s="9" t="s">
         <v>1808</v>
       </c>
@@ -34826,7 +34832,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A30" s="9" t="s">
         <v>1810</v>
       </c>
@@ -34867,7 +34873,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A31" s="9" t="s">
         <v>1812</v>
       </c>
@@ -34908,7 +34914,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A32" s="9" t="s">
         <v>1814</v>
       </c>
@@ -34949,7 +34955,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A33" s="9" t="s">
         <v>1816</v>
       </c>
@@ -34990,7 +34996,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A34" s="9" t="s">
         <v>1818</v>
       </c>
@@ -35031,7 +35037,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A35" s="9" t="s">
         <v>1820</v>
       </c>
@@ -35072,7 +35078,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A36" s="9" t="s">
         <v>1824</v>
       </c>
@@ -35113,7 +35119,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A37" s="9" t="s">
         <v>1827</v>
       </c>
@@ -35154,7 +35160,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A38" s="9" t="s">
         <v>1831</v>
       </c>
@@ -35195,7 +35201,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A39" s="9" t="s">
         <v>1834</v>
       </c>
@@ -35236,7 +35242,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A40" s="9" t="s">
         <v>1838</v>
       </c>
@@ -35277,7 +35283,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="41" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A41" s="8" t="s">
         <v>123</v>
       </c>
@@ -35294,7 +35300,7 @@
       <c r="L41" s="8"/>
       <c r="M41" s="8"/>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A42" s="9" t="s">
         <v>1841</v>
       </c>
@@ -35335,7 +35341,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A43" s="9" t="s">
         <v>1845</v>
       </c>
@@ -35376,7 +35382,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A44" s="9" t="s">
         <v>1849</v>
       </c>
@@ -35417,7 +35423,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A45" s="9" t="s">
         <v>1853</v>
       </c>
@@ -35458,7 +35464,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A46" s="9" t="s">
         <v>1857</v>
       </c>
@@ -35499,7 +35505,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A47" s="9" t="s">
         <v>1861</v>
       </c>
@@ -35540,7 +35546,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A48" s="9" t="s">
         <v>1865</v>
       </c>
@@ -35598,7 +35604,7 @@
       <c r="L49" s="7"/>
       <c r="M49" s="7"/>
     </row>
-    <row r="50" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="50" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A50" s="8" t="s">
         <v>22</v>
       </c>
@@ -35615,7 +35621,7 @@
       <c r="L50" s="8"/>
       <c r="M50" s="8"/>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A51" s="9" t="s">
         <v>1870</v>
       </c>
@@ -35656,7 +35662,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A52" s="9" t="s">
         <v>1872</v>
       </c>
@@ -35697,7 +35703,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A53" s="9" t="s">
         <v>1874</v>
       </c>
@@ -35738,7 +35744,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A54" s="9" t="s">
         <v>1876</v>
       </c>
@@ -35779,7 +35785,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A55" s="9" t="s">
         <v>1878</v>
       </c>
@@ -35820,7 +35826,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A56" s="9" t="s">
         <v>1880</v>
       </c>
@@ -35861,7 +35867,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A57" s="9" t="s">
         <v>1882</v>
       </c>
@@ -35902,7 +35908,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A58" s="9" t="s">
         <v>1886</v>
       </c>
@@ -35943,7 +35949,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A59" s="9" t="s">
         <v>1889</v>
       </c>
@@ -35984,7 +35990,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A60" s="9" t="s">
         <v>1893</v>
       </c>
@@ -36025,7 +36031,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A61" s="9" t="s">
         <v>1896</v>
       </c>
@@ -36066,7 +36072,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A62" s="9" t="s">
         <v>1900</v>
       </c>
@@ -36107,7 +36113,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A63" s="9" t="s">
         <v>1903</v>
       </c>
@@ -36148,7 +36154,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A64" s="9" t="s">
         <v>1907</v>
       </c>
@@ -36189,7 +36195,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A65" s="9" t="s">
         <v>1910</v>
       </c>
@@ -36230,7 +36236,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A66" s="9" t="s">
         <v>1914</v>
       </c>
@@ -36271,7 +36277,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A67" s="9" t="s">
         <v>1917</v>
       </c>
@@ -36312,7 +36318,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A68" s="9" t="s">
         <v>1921</v>
       </c>
@@ -36353,7 +36359,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="69" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="69" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A69" s="8" t="s">
         <v>123</v>
       </c>
@@ -36370,7 +36376,7 @@
       <c r="L69" s="8"/>
       <c r="M69" s="8"/>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A70" s="9" t="s">
         <v>1924</v>
       </c>
@@ -36411,7 +36417,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A71" s="9" t="s">
         <v>1928</v>
       </c>
@@ -36452,7 +36458,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A72" s="9" t="s">
         <v>1932</v>
       </c>
@@ -36493,7 +36499,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A73" s="9" t="s">
         <v>1936</v>
       </c>
@@ -36534,7 +36540,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A74" s="9" t="s">
         <v>1940</v>
       </c>
@@ -36575,7 +36581,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A75" s="9" t="s">
         <v>1944</v>
       </c>
@@ -36633,7 +36639,7 @@
       <c r="L76" s="7"/>
       <c r="M76" s="7"/>
     </row>
-    <row r="77" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="77" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A77" s="8" t="s">
         <v>22</v>
       </c>
@@ -36650,7 +36656,7 @@
       <c r="L77" s="8"/>
       <c r="M77" s="8"/>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A78" s="9" t="s">
         <v>1949</v>
       </c>
@@ -36691,7 +36697,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A79" s="9" t="s">
         <v>1951</v>
       </c>
@@ -36732,7 +36738,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A80" s="9" t="s">
         <v>1953</v>
       </c>
@@ -36773,7 +36779,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A81" s="9" t="s">
         <v>1955</v>
       </c>
@@ -36814,7 +36820,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A82" s="9" t="s">
         <v>1957</v>
       </c>
@@ -36855,7 +36861,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A83" s="9" t="s">
         <v>1959</v>
       </c>
@@ -36896,7 +36902,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A84" s="9" t="s">
         <v>1961</v>
       </c>
@@ -36937,7 +36943,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A85" s="9" t="s">
         <v>1965</v>
       </c>
@@ -36978,7 +36984,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A86" s="9" t="s">
         <v>1968</v>
       </c>
@@ -37019,7 +37025,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A87" s="9" t="s">
         <v>1972</v>
       </c>
@@ -37060,7 +37066,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A88" s="9" t="s">
         <v>1975</v>
       </c>
@@ -37101,7 +37107,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A89" s="9" t="s">
         <v>1979</v>
       </c>
@@ -37142,7 +37148,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A90" s="9" t="s">
         <v>1982</v>
       </c>
@@ -37183,7 +37189,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A91" s="9" t="s">
         <v>1986</v>
       </c>
@@ -37224,7 +37230,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A92" s="9" t="s">
         <v>1989</v>
       </c>
@@ -37265,7 +37271,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A93" s="9" t="s">
         <v>1993</v>
       </c>
@@ -37306,7 +37312,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A94" s="9" t="s">
         <v>1996</v>
       </c>
@@ -37347,7 +37353,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A95" s="9" t="s">
         <v>2000</v>
       </c>
@@ -37388,7 +37394,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="96" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="96" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A96" s="8" t="s">
         <v>123</v>
       </c>
@@ -37405,7 +37411,7 @@
       <c r="L96" s="8"/>
       <c r="M96" s="8"/>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A97" s="9" t="s">
         <v>2003</v>
       </c>
@@ -37446,7 +37452,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A98" s="9" t="s">
         <v>2007</v>
       </c>
@@ -37487,7 +37493,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A99" s="9" t="s">
         <v>2011</v>
       </c>
@@ -37545,7 +37551,7 @@
       <c r="L100" s="7"/>
       <c r="M100" s="7"/>
     </row>
-    <row r="101" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="101" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A101" s="8" t="s">
         <v>22</v>
       </c>
@@ -37562,7 +37568,7 @@
       <c r="L101" s="8"/>
       <c r="M101" s="8"/>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A102" s="9" t="s">
         <v>2016</v>
       </c>
@@ -37603,7 +37609,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A103" s="9" t="s">
         <v>2018</v>
       </c>
@@ -37644,7 +37650,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A104" s="9" t="s">
         <v>2020</v>
       </c>
@@ -37685,7 +37691,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A105" s="9" t="s">
         <v>2022</v>
       </c>
@@ -37726,7 +37732,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A106" s="9" t="s">
         <v>2024</v>
       </c>
@@ -37767,7 +37773,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A107" s="9" t="s">
         <v>2026</v>
       </c>
@@ -37808,7 +37814,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A108" s="9" t="s">
         <v>2028</v>
       </c>
@@ -37849,7 +37855,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A109" s="9" t="s">
         <v>2032</v>
       </c>
@@ -37890,7 +37896,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="110" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="110" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A110" s="8" t="s">
         <v>123</v>
       </c>
@@ -37907,7 +37913,7 @@
       <c r="L110" s="8"/>
       <c r="M110" s="8"/>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A111" s="9" t="s">
         <v>2035</v>
       </c>
@@ -37948,7 +37954,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A112" s="9" t="s">
         <v>2039</v>
       </c>
@@ -38006,7 +38012,7 @@
       <c r="L113" s="7"/>
       <c r="M113" s="7"/>
     </row>
-    <row r="114" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="114" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A114" s="8" t="s">
         <v>22</v>
       </c>
@@ -38023,7 +38029,7 @@
       <c r="L114" s="8"/>
       <c r="M114" s="8"/>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A115" s="9" t="s">
         <v>2044</v>
       </c>
@@ -38064,7 +38070,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A116" s="9" t="s">
         <v>2046</v>
       </c>
@@ -38105,7 +38111,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A117" s="9" t="s">
         <v>2048</v>
       </c>
@@ -38146,7 +38152,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A118" s="9" t="s">
         <v>2050</v>
       </c>
@@ -38187,7 +38193,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A119" s="9" t="s">
         <v>2052</v>
       </c>
@@ -38228,7 +38234,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A120" s="9" t="s">
         <v>2054</v>
       </c>
@@ -38269,7 +38275,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A121" s="9" t="s">
         <v>2056</v>
       </c>
@@ -38310,7 +38316,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A122" s="9" t="s">
         <v>2060</v>
       </c>
@@ -38351,7 +38357,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A123" s="9" t="s">
         <v>2063</v>
       </c>
@@ -38392,7 +38398,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A124" s="9" t="s">
         <v>2067</v>
       </c>
@@ -38433,7 +38439,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A125" s="9" t="s">
         <v>2070</v>
       </c>
@@ -38474,7 +38480,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A126" s="9" t="s">
         <v>2074</v>
       </c>
@@ -38515,7 +38521,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="127" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="127" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A127" s="8" t="s">
         <v>123</v>
       </c>
@@ -38532,7 +38538,7 @@
       <c r="L127" s="8"/>
       <c r="M127" s="8"/>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A128" s="9" t="s">
         <v>2077</v>
       </c>
@@ -38573,7 +38579,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A129" s="9" t="s">
         <v>2081</v>
       </c>
@@ -38631,7 +38637,7 @@
       <c r="L130" s="7"/>
       <c r="M130" s="7"/>
     </row>
-    <row r="131" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="131" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A131" s="8" t="s">
         <v>22</v>
       </c>
@@ -38648,7 +38654,7 @@
       <c r="L131" s="8"/>
       <c r="M131" s="8"/>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A132" s="9" t="s">
         <v>2086</v>
       </c>
@@ -38689,7 +38695,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A133" s="9" t="s">
         <v>2088</v>
       </c>
@@ -38730,7 +38736,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A134" s="9" t="s">
         <v>2090</v>
       </c>
@@ -38771,7 +38777,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A135" s="9" t="s">
         <v>2092</v>
       </c>
@@ -38812,7 +38818,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A136" s="9" t="s">
         <v>2094</v>
       </c>
@@ -38853,7 +38859,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A137" s="9" t="s">
         <v>2096</v>
       </c>
@@ -38894,7 +38900,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A138" s="9" t="s">
         <v>2098</v>
       </c>
@@ -38935,7 +38941,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A139" s="9" t="s">
         <v>2102</v>
       </c>
@@ -38976,7 +38982,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A140" s="9" t="s">
         <v>2105</v>
       </c>
@@ -39017,7 +39023,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A141" s="9" t="s">
         <v>2109</v>
       </c>
@@ -39058,7 +39064,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="142" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="142" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A142" s="8" t="s">
         <v>123</v>
       </c>
@@ -39075,7 +39081,7 @@
       <c r="L142" s="8"/>
       <c r="M142" s="8"/>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A143" s="9" t="s">
         <v>2112</v>
       </c>
@@ -39116,7 +39122,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A144" s="9" t="s">
         <v>2116</v>
       </c>
@@ -39174,7 +39180,7 @@
       <c r="L145" s="7"/>
       <c r="M145" s="7"/>
     </row>
-    <row r="146" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="146" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A146" s="8" t="s">
         <v>22</v>
       </c>
@@ -39191,7 +39197,7 @@
       <c r="L146" s="8"/>
       <c r="M146" s="8"/>
     </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A147" s="9" t="s">
         <v>2121</v>
       </c>
@@ -39232,7 +39238,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A148" s="9" t="s">
         <v>2123</v>
       </c>
@@ -39273,7 +39279,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A149" s="9" t="s">
         <v>2125</v>
       </c>
@@ -39314,7 +39320,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A150" s="9" t="s">
         <v>2127</v>
       </c>
@@ -39355,7 +39361,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A151" s="9" t="s">
         <v>2129</v>
       </c>
@@ -39396,7 +39402,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A152" s="9" t="s">
         <v>2131</v>
       </c>
@@ -39437,7 +39443,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A153" s="9" t="s">
         <v>2133</v>
       </c>
@@ -39478,7 +39484,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A154" s="9" t="s">
         <v>2137</v>
       </c>
@@ -39519,7 +39525,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A155" s="9" t="s">
         <v>2140</v>
       </c>
@@ -39560,7 +39566,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A156" s="9" t="s">
         <v>2144</v>
       </c>
@@ -39601,7 +39607,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A157" s="9" t="s">
         <v>2147</v>
       </c>
@@ -39642,7 +39648,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A158" s="9" t="s">
         <v>2151</v>
       </c>
@@ -39683,7 +39689,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A159" s="9" t="s">
         <v>2154</v>
       </c>
@@ -39724,7 +39730,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A160" s="9" t="s">
         <v>2158</v>
       </c>
@@ -39765,7 +39771,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="161" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="161" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A161" s="8" t="s">
         <v>123</v>
       </c>
@@ -39782,7 +39788,7 @@
       <c r="L161" s="8"/>
       <c r="M161" s="8"/>
     </row>
-    <row r="162" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A162" s="9" t="s">
         <v>2162</v>
       </c>
@@ -39823,7 +39829,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A163" s="9" t="s">
         <v>2166</v>
       </c>
@@ -39864,7 +39870,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A164" s="9" t="s">
         <v>2170</v>
       </c>
@@ -39905,7 +39911,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A165" s="9" t="s">
         <v>2174</v>
       </c>
@@ -39946,7 +39952,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="166" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A166" s="9" t="s">
         <v>2177</v>
       </c>
@@ -39987,7 +39993,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="167" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A167" s="9" t="s">
         <v>2181</v>
       </c>
@@ -40045,7 +40051,7 @@
       <c r="L168" s="7"/>
       <c r="M168" s="7"/>
     </row>
-    <row r="169" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="169" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A169" s="8" t="s">
         <v>22</v>
       </c>
@@ -40062,7 +40068,7 @@
       <c r="L169" s="8"/>
       <c r="M169" s="8"/>
     </row>
-    <row r="170" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A170" s="9" t="s">
         <v>2186</v>
       </c>
@@ -40103,7 +40109,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="171" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A171" s="9" t="s">
         <v>2188</v>
       </c>
@@ -40144,7 +40150,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="172" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A172" s="9" t="s">
         <v>2190</v>
       </c>
@@ -40185,7 +40191,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="173" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A173" s="9" t="s">
         <v>2192</v>
       </c>
@@ -40226,7 +40232,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="174" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A174" s="9" t="s">
         <v>2194</v>
       </c>
@@ -40267,7 +40273,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="175" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A175" s="9" t="s">
         <v>2196</v>
       </c>
@@ -40308,7 +40314,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="176" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A176" s="9" t="s">
         <v>2198</v>
       </c>
@@ -40349,7 +40355,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A177" s="9" t="s">
         <v>2202</v>
       </c>
@@ -40390,7 +40396,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="178" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A178" s="9" t="s">
         <v>2205</v>
       </c>
@@ -40431,7 +40437,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="179" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A179" s="9" t="s">
         <v>2209</v>
       </c>
@@ -40472,7 +40478,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A180" s="9" t="s">
         <v>2212</v>
       </c>
@@ -40513,7 +40519,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="181" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A181" s="9" t="s">
         <v>2216</v>
       </c>
@@ -40554,7 +40560,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="182" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="182" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A182" s="8" t="s">
         <v>123</v>
       </c>
@@ -40571,7 +40577,7 @@
       <c r="L182" s="8"/>
       <c r="M182" s="8"/>
     </row>
-    <row r="183" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A183" s="9" t="s">
         <v>2219</v>
       </c>
@@ -40612,7 +40618,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="184" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A184" s="9" t="s">
         <v>2223</v>
       </c>
@@ -40670,7 +40676,7 @@
       <c r="L185" s="7"/>
       <c r="M185" s="7"/>
     </row>
-    <row r="186" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="186" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A186" s="8" t="s">
         <v>22</v>
       </c>
@@ -40687,7 +40693,7 @@
       <c r="L186" s="8"/>
       <c r="M186" s="8"/>
     </row>
-    <row r="187" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A187" s="9" t="s">
         <v>2228</v>
       </c>
@@ -40728,7 +40734,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="188" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A188" s="9" t="s">
         <v>2230</v>
       </c>
@@ -40769,7 +40775,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="189" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A189" s="9" t="s">
         <v>2232</v>
       </c>
@@ -40810,7 +40816,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="190" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A190" s="9" t="s">
         <v>2234</v>
       </c>
@@ -40851,7 +40857,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="191" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A191" s="9" t="s">
         <v>2236</v>
       </c>
@@ -40892,7 +40898,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="192" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A192" s="9" t="s">
         <v>2238</v>
       </c>
@@ -40933,7 +40939,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="193" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A193" s="9" t="s">
         <v>2240</v>
       </c>
@@ -40974,7 +40980,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="194" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A194" s="9" t="s">
         <v>2244</v>
       </c>
@@ -41015,7 +41021,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="195" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A195" s="9" t="s">
         <v>2247</v>
       </c>
@@ -41056,7 +41062,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="196" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A196" s="9" t="s">
         <v>2251</v>
       </c>
@@ -41097,7 +41103,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="197" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="197" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A197" s="8" t="s">
         <v>123</v>
       </c>
@@ -41114,7 +41120,7 @@
       <c r="L197" s="8"/>
       <c r="M197" s="8"/>
     </row>
-    <row r="198" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A198" s="9" t="s">
         <v>2254</v>
       </c>
@@ -41172,7 +41178,7 @@
       <c r="L199" s="7"/>
       <c r="M199" s="7"/>
     </row>
-    <row r="200" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="200" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A200" s="8" t="s">
         <v>22</v>
       </c>
@@ -41189,7 +41195,7 @@
       <c r="L200" s="8"/>
       <c r="M200" s="8"/>
     </row>
-    <row r="201" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A201" s="9" t="s">
         <v>2259</v>
       </c>
@@ -41230,7 +41236,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="202" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A202" s="9" t="s">
         <v>2261</v>
       </c>
@@ -41271,7 +41277,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="203" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A203" s="9" t="s">
         <v>2263</v>
       </c>
@@ -41312,7 +41318,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="204" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A204" s="9" t="s">
         <v>2265</v>
       </c>
@@ -41353,7 +41359,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="205" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A205" s="9" t="s">
         <v>2267</v>
       </c>
@@ -41394,7 +41400,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="206" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A206" s="9" t="s">
         <v>2269</v>
       </c>
@@ -41435,7 +41441,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="207" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A207" s="9" t="s">
         <v>2271</v>
       </c>
@@ -41476,7 +41482,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="208" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A208" s="9" t="s">
         <v>2275</v>
       </c>
@@ -41517,7 +41523,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="209" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A209" s="9" t="s">
         <v>2278</v>
       </c>
@@ -41558,7 +41564,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="210" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A210" s="9" t="s">
         <v>2282</v>
       </c>
@@ -41599,7 +41605,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="211" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="211" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A211" s="8" t="s">
         <v>123</v>
       </c>
@@ -41616,7 +41622,7 @@
       <c r="L211" s="8"/>
       <c r="M211" s="8"/>
     </row>
-    <row r="212" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A212" s="9" t="s">
         <v>2285</v>
       </c>
@@ -41710,6 +41716,9 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
   <dimension ref="A1:M39"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
@@ -41863,7 +41872,7 @@
       <c r="L12" s="7"/>
       <c r="M12" s="7"/>
     </row>
-    <row r="13" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A13" s="8" t="s">
         <v>123</v>
       </c>
@@ -41880,7 +41889,7 @@
       <c r="L13" s="8"/>
       <c r="M13" s="8"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A14" s="9" t="s">
         <v>2291</v>
       </c>
@@ -41921,7 +41930,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A15" s="9" t="s">
         <v>2295</v>
       </c>
@@ -41962,7 +41971,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A16" s="9" t="s">
         <v>2299</v>
       </c>
@@ -42003,7 +42012,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A17" s="9" t="s">
         <v>2303</v>
       </c>
@@ -42044,7 +42053,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A18" s="9" t="s">
         <v>2307</v>
       </c>
@@ -42085,7 +42094,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A19" s="9" t="s">
         <v>2311</v>
       </c>
@@ -42126,7 +42135,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A20" s="9" t="s">
         <v>2315</v>
       </c>
@@ -42167,7 +42176,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A21" s="9" t="s">
         <v>2319</v>
       </c>
@@ -42208,7 +42217,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A22" s="9" t="s">
         <v>2323</v>
       </c>
@@ -42249,7 +42258,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A23" s="9" t="s">
         <v>2327</v>
       </c>
@@ -42290,7 +42299,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A24" s="9" t="s">
         <v>2331</v>
       </c>
@@ -42331,7 +42340,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A25" s="9" t="s">
         <v>2335</v>
       </c>
@@ -42372,7 +42381,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A26" s="9" t="s">
         <v>2339</v>
       </c>
@@ -42413,7 +42422,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A27" s="9" t="s">
         <v>2343</v>
       </c>
@@ -42454,7 +42463,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A28" s="9" t="s">
         <v>2347</v>
       </c>
@@ -42495,7 +42504,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A29" s="9" t="s">
         <v>2351</v>
       </c>
@@ -42536,7 +42545,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A30" s="9" t="s">
         <v>2355</v>
       </c>
@@ -42577,7 +42586,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A31" s="9" t="s">
         <v>2359</v>
       </c>
@@ -42618,7 +42627,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A32" s="9" t="s">
         <v>2363</v>
       </c>
@@ -42659,7 +42668,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A33" s="9" t="s">
         <v>2367</v>
       </c>
@@ -42700,7 +42709,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A34" s="9" t="s">
         <v>2371</v>
       </c>
@@ -42741,7 +42750,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A35" s="9" t="s">
         <v>2375</v>
       </c>
@@ -42782,7 +42791,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A36" s="9" t="s">
         <v>2379</v>
       </c>
@@ -42823,7 +42832,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A37" s="9" t="s">
         <v>2383</v>
       </c>
@@ -42864,7 +42873,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A38" s="9" t="s">
         <v>2387</v>
       </c>
@@ -42905,7 +42914,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A39" s="9" t="s">
         <v>2391</v>
       </c>
@@ -42968,6 +42977,9 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
@@ -43121,7 +43133,7 @@
       <c r="L12" s="7"/>
       <c r="M12" s="7"/>
     </row>
-    <row r="13" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A13" s="8" t="s">
         <v>2397</v>
       </c>
@@ -43138,7 +43150,7 @@
       <c r="L13" s="8"/>
       <c r="M13" s="8"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A14" s="9" t="s">
         <v>2398</v>
       </c>
@@ -43179,7 +43191,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A15" s="9" t="s">
         <v>2402</v>
       </c>
@@ -43220,7 +43232,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A16" s="9" t="s">
         <v>2406</v>
       </c>
@@ -43261,7 +43273,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A17" s="9" t="s">
         <v>2410</v>
       </c>
@@ -43302,7 +43314,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A18" s="9" t="s">
         <v>2414</v>
       </c>
@@ -43343,7 +43355,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A19" s="9" t="s">
         <v>2418</v>
       </c>
@@ -43384,7 +43396,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A20" s="9" t="s">
         <v>2422</v>
       </c>
@@ -43425,7 +43437,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A21" s="9" t="s">
         <v>2426</v>
       </c>
@@ -43466,7 +43478,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A22" s="9" t="s">
         <v>2430</v>
       </c>
@@ -43507,7 +43519,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A23" s="9" t="s">
         <v>2434</v>
       </c>
@@ -43548,7 +43560,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A24" s="9" t="s">
         <v>2438</v>
       </c>
@@ -43589,7 +43601,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25" outlineLevel="2" collapsed="1">
       <c r="A25" s="9" t="s">
         <v>2442</v>
       </c>
